--- a/context_DB/MLI_context_db.xlsx
+++ b/context_DB/MLI_context_db.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL46"/>
+  <dimension ref="A1:BM46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -686,65 +686,70 @@
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
+          <t>fatalities</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>event_count_evt2</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>ADM1_PCODE_evt2</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>ADM3_PCODE_evt2</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>event_type</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>sub_event_type</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>actor1</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>assoc_actor_1</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>actor2</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>assoc_actor_2</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>event_date</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
           <t>admin2</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>fatalities</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>event_count_evt2</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>ADM3_PCODE_evt2</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>event_type</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>sub_event_type</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>actor1</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>assoc_actor_1</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>actor2</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>assoc_actor_2</t>
-        </is>
-      </c>
-      <c r="BJ1" s="1" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="BK1" s="1" t="inlineStr">
-        <is>
-          <t>event_date</t>
-        </is>
-      </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>ratio IDP/ToTN - HPC2025</t>
         </is>
@@ -858,7 +863,8 @@
       <c r="BI2" t="inlineStr"/>
       <c r="BJ2" t="inlineStr"/>
       <c r="BK2" t="inlineStr"/>
-      <c r="BL2" t="n">
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -962,16 +968,16 @@
           <t>Kayes</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>Kayes</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="n">
         <v>1</v>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>ML01</t>
+        </is>
       </c>
       <c r="BC3" t="inlineStr"/>
       <c r="BD3" t="inlineStr">
@@ -999,10 +1005,15 @@
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>28 February 2025</t>
-        </is>
-      </c>
-      <c r="BL3" t="n">
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>Kayes</t>
+        </is>
+      </c>
+      <c r="BM3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1104,7 +1115,8 @@
       <c r="BI4" t="inlineStr"/>
       <c r="BJ4" t="inlineStr"/>
       <c r="BK4" t="inlineStr"/>
-      <c r="BL4" t="n">
+      <c r="BL4" t="inlineStr"/>
+      <c r="BM4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1198,16 +1210,16 @@
           <t>Kayes</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>Kita</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB5" t="n">
         <v>1</v>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>ML01</t>
+        </is>
       </c>
       <c r="BC5" t="inlineStr"/>
       <c r="BD5" t="inlineStr">
@@ -1243,10 +1255,15 @@
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>07 March 2024</t>
-        </is>
-      </c>
-      <c r="BL5" t="n">
+          <t>2024-03-07</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>Kita</t>
+        </is>
+      </c>
+      <c r="BM5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1358,7 +1375,8 @@
       <c r="BI6" t="inlineStr"/>
       <c r="BJ6" t="inlineStr"/>
       <c r="BK6" t="inlineStr"/>
-      <c r="BL6" t="n">
+      <c r="BL6" t="inlineStr"/>
+      <c r="BM6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1470,7 +1488,8 @@
       <c r="BI7" t="inlineStr"/>
       <c r="BJ7" t="inlineStr"/>
       <c r="BK7" t="inlineStr"/>
-      <c r="BL7" t="n">
+      <c r="BL7" t="inlineStr"/>
+      <c r="BM7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1582,7 +1601,8 @@
       <c r="BI8" t="inlineStr"/>
       <c r="BJ8" t="inlineStr"/>
       <c r="BK8" t="inlineStr"/>
-      <c r="BL8" t="n">
+      <c r="BL8" t="inlineStr"/>
+      <c r="BM8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1756,7 +1776,8 @@
       <c r="BI9" t="inlineStr"/>
       <c r="BJ9" t="inlineStr"/>
       <c r="BK9" t="inlineStr"/>
-      <c r="BL9" t="n">
+      <c r="BL9" t="inlineStr"/>
+      <c r="BM9" t="n">
         <v>0.1770941054808687</v>
       </c>
     </row>
@@ -1868,7 +1889,8 @@
       <c r="BI10" t="inlineStr"/>
       <c r="BJ10" t="inlineStr"/>
       <c r="BK10" t="inlineStr"/>
-      <c r="BL10" t="n">
+      <c r="BL10" t="inlineStr"/>
+      <c r="BM10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1980,7 +2002,8 @@
       <c r="BI11" t="inlineStr"/>
       <c r="BJ11" t="inlineStr"/>
       <c r="BK11" t="inlineStr"/>
-      <c r="BL11" t="n">
+      <c r="BL11" t="inlineStr"/>
+      <c r="BM11" t="n">
         <v>0.1738623103850642</v>
       </c>
     </row>
@@ -2092,7 +2115,8 @@
       <c r="BI12" t="inlineStr"/>
       <c r="BJ12" t="inlineStr"/>
       <c r="BK12" t="inlineStr"/>
-      <c r="BL12" t="n">
+      <c r="BL12" t="inlineStr"/>
+      <c r="BM12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2196,31 +2220,31 @@
           <t>Koulikoro</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>Koulikoro</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB13" t="n">
         <v>5</v>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>ML02</t>
+        </is>
       </c>
       <c r="BC13" t="inlineStr"/>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>Protests ---- Protests ---- Protests ---- Protests ---- Strategic developments</t>
+          <t>Strategic developments ---- Protests ---- Protests ---- Protests ---- Protests</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Looting/property destruction</t>
+          <t>Looting/property destruction ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>Protesters (Mali) ---- Protesters (Mali) ---- Protesters (Mali) ---- Protesters (Mali) ---- JNIM: Group for Support of Islam and Muslims</t>
+          <t>JNIM: Group for Support of Islam and Muslims ---- Protesters (Mali) ---- Protesters (Mali) ---- Protesters (Mali) ---- Protesters (Mali)</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
@@ -2240,15 +2264,20 @@
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>On 5 August 2024, students from the rural polytechnic institute for training and applied research (IPR/IFRA) staged a peaceful demonstration in the town of Koulikoro (Koulikoro, Koulikoro). They protested against the death of a student in a traffic accident on the Bamako-Koulikoro road. According to the demonstration organizers, the student was on his way to a make-up exam. The students claimed that all make-up exams be held on the Institute's premises in Katibougou, in the urban commune of Koulikoro. ---- On 25 January 2024, a number of students from the Katibougou Rural Polytechnic Institute staged a 120-hours demonstration (started on 23 January) in Katibougou (Koulikoro, Koulikoro) to denounce the land predation that threatens the university spaces at their institute. They also demanded the resumption of their university infrastructure construction work interrupted by the inhabitants of the village Katibougou. ---- On 24 January 2024, a number of students from the Katibougou Rural Polytechnic Institute staged a 120-hours demonstration (started on 23 January) in Katibougou (Koulikoro, Koulikoro) to denounce the land predation that threatens the university spaces at their institute. They also demanded the resumption of their university infrastructure construction work interrupted by the inhabitants of the village Katibougou. ---- On 23 January 2024, a number of students from the Katibougou Rural Polytechnic Institute staged a 120-hours demonstration in Katibougou (Koulikoro, Koulikoro) to denounce the land predation that threatens the university spaces at their institute. They also demanded the resumption of their university infrastructure construction work interrupted by the inhabitants of the village Katibougou. ---- Property destruction: On 13 January 2024, JNIM militants set fire to the management of the Koula school (Dioila, Koulikoro). The militants also prohibited the populations of Koula from crossing the river to the village of Beleko.</t>
+          <t>Property destruction: On 13 January 2024, JNIM militants set fire to the management of the Koula school (Dioila, Koulikoro). The militants also prohibited the populations of Koula from crossing the river to the village of Beleko. ---- On 23 January 2024, a number of students from the Katibougou Rural Polytechnic Institute staged a 120-hours demonstration in Katibougou (Koulikoro, Koulikoro) to denounce the land predation that threatens the university spaces at their institute. They also demanded the resumption of their university infrastructure construction work interrupted by the inhabitants of the village Katibougou. ---- On 24 January 2024, a number of students from the Katibougou Rural Polytechnic Institute staged a 120-hours demonstration (started on 23 January) in Katibougou (Koulikoro, Koulikoro) to denounce the land predation that threatens the university spaces at their institute. They also demanded the resumption of their university infrastructure construction work interrupted by the inhabitants of the village Katibougou. ---- On 25 January 2024, a number of students from the Katibougou Rural Polytechnic Institute staged a 120-hours demonstration (started on 23 January) in Katibougou (Koulikoro, Koulikoro) to denounce the land predation that threatens the university spaces at their institute. They also demanded the resumption of their university infrastructure construction work interrupted by the inhabitants of the village Katibougou. ---- On 5 August 2024, students from the rural polytechnic institute for training and applied research (IPR/IFRA) staged a peaceful demonstration in the town of Koulikoro (Koulikoro, Koulikoro). They protested against the death of a student in a traffic accident on the Bamako-Koulikoro road. According to the demonstration organizers, the student was on his way to a make-up exam. The students claimed that all make-up exams be held on the Institute's premises in Katibougou, in the urban commune of Koulikoro.</t>
         </is>
       </c>
       <c r="BK13" t="inlineStr">
         <is>
-          <t>05 August 2024 ---- 25 January 2024 ---- 24 January 2024 ---- 23 January 2024 ---- 13 January 2024</t>
-        </is>
-      </c>
-      <c r="BL13" t="n">
+          <t>2024-01-13 ---- 2024-01-23 ---- 2024-01-24 ---- 2024-01-25 ---- 2024-08-05</t>
+        </is>
+      </c>
+      <c r="BL13" t="inlineStr">
+        <is>
+          <t>Koulikoro</t>
+        </is>
+      </c>
+      <c r="BM13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2360,7 +2389,8 @@
       <c r="BI14" t="inlineStr"/>
       <c r="BJ14" t="inlineStr"/>
       <c r="BK14" t="inlineStr"/>
-      <c r="BL14" t="n">
+      <c r="BL14" t="inlineStr"/>
+      <c r="BM14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2472,7 +2502,8 @@
       <c r="BI15" t="inlineStr"/>
       <c r="BJ15" t="inlineStr"/>
       <c r="BK15" t="inlineStr"/>
-      <c r="BL15" t="n">
+      <c r="BL15" t="inlineStr"/>
+      <c r="BM15" t="n">
         <v>0.18997668997669</v>
       </c>
     </row>
@@ -2576,31 +2607,31 @@
           <t>Sikasso</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>Sikasso</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB16" t="n">
         <v>2</v>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>ML03</t>
+        </is>
       </c>
       <c r="BC16" t="inlineStr"/>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>Protests ---- Battles</t>
+          <t>Battles ---- Protests</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>Peaceful protest ---- Armed clash</t>
+          <t>Armed clash ---- Peaceful protest</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>Protesters (Mali) ---- JNIM: Group for Support of Islam and Muslims</t>
+          <t>JNIM: Group for Support of Islam and Muslims ---- Protesters (Mali)</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
@@ -2616,15 +2647,20 @@
       <c r="BI16" t="inlineStr"/>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>On 3 March 2025, teachers staged a demonstration in the town of Niena (Sikasso, Sikasso) to demand the release of a member of the teachers' union arrested by the local Police. ---- On 13 February 2025, JNIM militants attacked a convoy of the Minister of Higher Education escorted by gendarmes between Darabougou and Niena (Sikasso, Sikasso), coded to Darabougou. The militants fired a rocket, followed by AK rifles fire. The attack was repulsed, and four gendarmes were injured. The convoy passed the incident place and reached the town of Niena.</t>
+          <t>On 13 February 2025, JNIM militants attacked a convoy of the Minister of Higher Education escorted by gendarmes between Darabougou and Niena (Sikasso, Sikasso), coded to Darabougou. The militants fired a rocket, followed by AK rifles fire. The attack was repulsed, and four gendarmes were injured. The convoy passed the incident place and reached the town of Niena. ---- On 3 March 2025, teachers staged a demonstration in the town of Niena (Sikasso, Sikasso) to demand the release of a member of the teachers' union arrested by the local Police.</t>
         </is>
       </c>
       <c r="BK16" t="inlineStr">
         <is>
-          <t>03 March 2025 ---- 13 February 2025</t>
-        </is>
-      </c>
-      <c r="BL16" t="n">
+          <t>2025-02-13 ---- 2025-03-03</t>
+        </is>
+      </c>
+      <c r="BL16" t="inlineStr">
+        <is>
+          <t>Sikasso</t>
+        </is>
+      </c>
+      <c r="BM16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2798,7 +2834,8 @@
       <c r="BI17" t="inlineStr"/>
       <c r="BJ17" t="inlineStr"/>
       <c r="BK17" t="inlineStr"/>
-      <c r="BL17" t="n">
+      <c r="BL17" t="inlineStr"/>
+      <c r="BM17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2910,7 +2947,8 @@
       <c r="BI18" t="inlineStr"/>
       <c r="BJ18" t="inlineStr"/>
       <c r="BK18" t="inlineStr"/>
-      <c r="BL18" t="n">
+      <c r="BL18" t="inlineStr"/>
+      <c r="BM18" t="n">
         <v>0.001673271686481726</v>
       </c>
     </row>
@@ -3022,7 +3060,8 @@
       <c r="BI19" t="inlineStr"/>
       <c r="BJ19" t="inlineStr"/>
       <c r="BK19" t="inlineStr"/>
-      <c r="BL19" t="n">
+      <c r="BL19" t="inlineStr"/>
+      <c r="BM19" t="n">
         <v>0.01949693019608941</v>
       </c>
     </row>
@@ -3192,16 +3231,16 @@
           <t>Segou</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>Macina</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>1</v>
       </c>
       <c r="BA20" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB20" t="n">
         <v>4</v>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>ML04</t>
+        </is>
       </c>
       <c r="BC20" t="inlineStr"/>
       <c r="BD20" t="inlineStr">
@@ -3211,12 +3250,12 @@
       </c>
       <c r="BE20" t="inlineStr">
         <is>
-          <t>Abduction/forced disappearance ---- Attack ---- Abduction/forced disappearance ---- Attack</t>
+          <t>Attack ---- Abduction/forced disappearance ---- Attack ---- Abduction/forced disappearance</t>
         </is>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>JNIM: Group for Support of Islam and Muslims ---- Military Forces of Mali (2021-) ---- JNIM: Group for Support of Islam and Muslims ---- JNIM: Group for Support of Islam and Muslims</t>
+          <t>JNIM: Group for Support of Islam and Muslims ---- JNIM: Group for Support of Islam and Muslims ---- Military Forces of Mali (2021-) ---- JNIM: Group for Support of Islam and Muslims</t>
         </is>
       </c>
       <c r="BG20" t="inlineStr"/>
@@ -3227,20 +3266,25 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>Teachers (Mali) ---- Pastoralists (Mali) ---- Teachers (Mali) ---- Teachers (Mali)</t>
+          <t>Teachers (Mali) ---- Teachers (Mali) ---- Pastoralists (Mali) ---- Teachers (Mali)</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>On 3 January 2025, an armed group (likely JNIM militants, based on location) abducted two teachers in the village of Tielan (Macina, Segou). ---- On 3 June 2024, soldiers securing the basic education diploma (DEF) exams fired heavily at cattle grazing along the irrigation canals of the Niger office and at the pastoralists in Kolongo Tomo (Macina, Segou). A pastoralist was killed, and animals were slaughtered. ---- On 6 January 2024, JNIM militants abducted two teachers in the village of Tielan (Macina, Segou). The abducted were released on 9 January. ---- On 3 January 2024, JNIM militants attacked the village of Tielan (Macina, Segou). The village was burned and two teachers were abducted. Casualties unknown.</t>
+          <t>On 3 January 2024, JNIM militants attacked the village of Tielan (Macina, Segou). The village was burned and two teachers were abducted. Casualties unknown. ---- On 6 January 2024, JNIM militants abducted two teachers in the village of Tielan (Macina, Segou). The abducted were released on 9 January. ---- On 3 June 2024, soldiers securing the basic education diploma (DEF) exams fired heavily at cattle grazing along the irrigation canals of the Niger office and at the pastoralists in Kolongo Tomo (Macina, Segou). A pastoralist was killed, and animals were slaughtered. ---- On 3 January 2025, an armed group (likely JNIM militants, based on location) abducted two teachers in the village of Tielan (Macina, Segou).</t>
         </is>
       </c>
       <c r="BK20" t="inlineStr">
         <is>
-          <t>03 January 2025 ---- 03 June 2024 ---- 06 January 2024 ---- 03 January 2024</t>
-        </is>
-      </c>
-      <c r="BL20" t="n">
+          <t>2024-01-03 ---- 2024-01-06 ---- 2024-06-03 ---- 2025-01-03</t>
+        </is>
+      </c>
+      <c r="BL20" t="inlineStr">
+        <is>
+          <t>Macina</t>
+        </is>
+      </c>
+      <c r="BM20" t="n">
         <v>0.04077413716312176</v>
       </c>
     </row>
@@ -3352,7 +3396,8 @@
       <c r="BI21" t="inlineStr"/>
       <c r="BJ21" t="inlineStr"/>
       <c r="BK21" t="inlineStr"/>
-      <c r="BL21" t="n">
+      <c r="BL21" t="inlineStr"/>
+      <c r="BM21" t="n">
         <v>0.04372566058382414</v>
       </c>
     </row>
@@ -3464,7 +3509,8 @@
       <c r="BI22" t="inlineStr"/>
       <c r="BJ22" t="inlineStr"/>
       <c r="BK22" t="inlineStr"/>
-      <c r="BL22" t="n">
+      <c r="BL22" t="inlineStr"/>
+      <c r="BM22" t="n">
         <v>0.02998954265356643</v>
       </c>
     </row>
@@ -3576,7 +3622,8 @@
       <c r="BI23" t="inlineStr"/>
       <c r="BJ23" t="inlineStr"/>
       <c r="BK23" t="inlineStr"/>
-      <c r="BL23" t="n">
+      <c r="BL23" t="inlineStr"/>
+      <c r="BM23" t="n">
         <v>0.1831748603590159</v>
       </c>
     </row>
@@ -3688,7 +3735,8 @@
       <c r="BI24" t="inlineStr"/>
       <c r="BJ24" t="inlineStr"/>
       <c r="BK24" t="inlineStr"/>
-      <c r="BL24" t="n">
+      <c r="BL24" t="inlineStr"/>
+      <c r="BM24" t="n">
         <v>0.02281301631899347</v>
       </c>
     </row>
@@ -3850,31 +3898,31 @@
           <t>Mopti</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>Bandiagara</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>1</v>
       </c>
       <c r="BA25" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB25" t="n">
         <v>2</v>
+      </c>
+      <c r="BB25" t="inlineStr">
+        <is>
+          <t>ML05</t>
+        </is>
       </c>
       <c r="BC25" t="inlineStr"/>
       <c r="BD25" t="inlineStr">
         <is>
-          <t>Violence against civilians ---- Protests</t>
+          <t>Protests ---- Violence against civilians</t>
         </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
-          <t>Attack ---- Peaceful protest</t>
+          <t>Peaceful protest ---- Attack</t>
         </is>
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>JNIM: Group for Support of Islam and Muslims ---- Protesters (Mali)</t>
+          <t>Protesters (Mali) ---- JNIM: Group for Support of Islam and Muslims</t>
         </is>
       </c>
       <c r="BG25" t="inlineStr">
@@ -3894,15 +3942,20 @@
       </c>
       <c r="BJ25" t="inlineStr">
         <is>
-          <t>On 25 August 2024, likely JNIM militants killed a teacher cultivating his field in Bandiagara (Bandiagara, Mopti). ---- On 17 January 2024, a number of students staged a demonstration in the town of Bandiagara (Bandiagara, Mopti) to denounce the lack of teachers at the public high school. The students called on the governor staff to find solutions.</t>
+          <t>On 17 January 2024, a number of students staged a demonstration in the town of Bandiagara (Bandiagara, Mopti) to denounce the lack of teachers at the public high school. The students called on the governor staff to find solutions. ---- On 25 August 2024, likely JNIM militants killed a teacher cultivating his field in Bandiagara (Bandiagara, Mopti).</t>
         </is>
       </c>
       <c r="BK25" t="inlineStr">
         <is>
-          <t>25 August 2024 ---- 17 January 2024</t>
-        </is>
-      </c>
-      <c r="BL25" t="n">
+          <t>2024-01-17 ---- 2024-08-25</t>
+        </is>
+      </c>
+      <c r="BL25" t="inlineStr">
+        <is>
+          <t>Bandiagara</t>
+        </is>
+      </c>
+      <c r="BM25" t="n">
         <v>0.09289959336878323</v>
       </c>
     </row>
@@ -4014,7 +4067,8 @@
       <c r="BI26" t="inlineStr"/>
       <c r="BJ26" t="inlineStr"/>
       <c r="BK26" t="inlineStr"/>
-      <c r="BL26" t="n">
+      <c r="BL26" t="inlineStr"/>
+      <c r="BM26" t="n">
         <v>0.0795547108335596</v>
       </c>
     </row>
@@ -4126,7 +4180,8 @@
       <c r="BI27" t="inlineStr"/>
       <c r="BJ27" t="inlineStr"/>
       <c r="BK27" t="inlineStr"/>
-      <c r="BL27" t="n">
+      <c r="BL27" t="inlineStr"/>
+      <c r="BM27" t="n">
         <v>0.01520097113568924</v>
       </c>
     </row>
@@ -4230,16 +4285,16 @@
           <t>Mopti</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>Douentza</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>13</v>
       </c>
       <c r="BA28" t="n">
-        <v>13</v>
-      </c>
-      <c r="BB28" t="n">
         <v>1</v>
+      </c>
+      <c r="BB28" t="inlineStr">
+        <is>
+          <t>ML05</t>
+        </is>
       </c>
       <c r="BC28" t="inlineStr"/>
       <c r="BD28" t="inlineStr">
@@ -4275,10 +4330,15 @@
       </c>
       <c r="BK28" t="inlineStr">
         <is>
-          <t>22 March 2024</t>
-        </is>
-      </c>
-      <c r="BL28" t="n">
+          <t>2024-03-22</t>
+        </is>
+      </c>
+      <c r="BL28" t="inlineStr">
+        <is>
+          <t>Douentza</t>
+        </is>
+      </c>
+      <c r="BM28" t="n">
         <v>0.001476701619408078</v>
       </c>
     </row>
@@ -4382,16 +4442,16 @@
           <t>Mopti</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>Koro</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>0</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB29" t="n">
         <v>1</v>
+      </c>
+      <c r="BB29" t="inlineStr">
+        <is>
+          <t>ML05</t>
+        </is>
       </c>
       <c r="BC29" t="inlineStr"/>
       <c r="BD29" t="inlineStr">
@@ -4423,10 +4483,15 @@
       </c>
       <c r="BK29" t="inlineStr">
         <is>
-          <t>23 February 2024</t>
-        </is>
-      </c>
-      <c r="BL29" t="n">
+          <t>2024-02-23</t>
+        </is>
+      </c>
+      <c r="BL29" t="inlineStr">
+        <is>
+          <t>Koro</t>
+        </is>
+      </c>
+      <c r="BM29" t="n">
         <v>0.02566964285714286</v>
       </c>
     </row>
@@ -4530,31 +4595,31 @@
           <t>Mopti</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>Mopti</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>3</v>
       </c>
       <c r="BA30" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB30" t="n">
         <v>4</v>
+      </c>
+      <c r="BB30" t="inlineStr">
+        <is>
+          <t>ML05</t>
+        </is>
       </c>
       <c r="BC30" t="inlineStr"/>
       <c r="BD30" t="inlineStr">
         <is>
-          <t>Violence against civilians ---- Violence against civilians ---- Violence against civilians ---- Strategic developments</t>
+          <t>Strategic developments ---- Violence against civilians ---- Violence against civilians ---- Violence against civilians</t>
         </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
-          <t>Attack ---- Abduction/forced disappearance ---- Attack ---- Arrests</t>
+          <t>Arrests ---- Attack ---- Abduction/forced disappearance ---- Attack</t>
         </is>
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>JNIM: Group for Support of Islam and Muslims ---- JNIM: Group for Support of Islam and Muslims ---- JNIM: Group for Support of Islam and Muslims ---- Military Forces of Mali (2021-)</t>
+          <t>Military Forces of Mali (2021-) ---- JNIM: Group for Support of Islam and Muslims ---- JNIM: Group for Support of Islam and Muslims ---- JNIM: Group for Support of Islam and Muslims</t>
         </is>
       </c>
       <c r="BG30" t="inlineStr">
@@ -4569,20 +4634,25 @@
       </c>
       <c r="BI30" t="inlineStr">
         <is>
-          <t>Muslim Group (Mali) ---- Muslim Group (Mali) ---- Muslim Group (Mali) ---- Fulani Ethnic Group (Mali); Pastoralists (Mali); Students (Mali)</t>
+          <t>Fulani Ethnic Group (Mali); Pastoralists (Mali); Students (Mali) ---- Muslim Group (Mali) ---- Muslim Group (Mali) ---- Muslim Group (Mali)</t>
         </is>
       </c>
       <c r="BJ30" t="inlineStr">
         <is>
-          <t>On 9 November 2024, JNIM militants killed two adolescent Quranic school students (Talibes) in the village of Niakongo (Mopti, Mopti). ---- On 31 October 2024, JNIM militants abducted a coranic school teacher in Sevare (Mopti, Mopti) ---- Around 15 August 2024 (month of), JNIM militants killed at least one adolescent Quranic school student (Talibe) in the village of Niakongo (Mopti, Mopti). ---- On 5 March 2024, FAMA and Wagner forces arrested several students from Fulani community in the town of Sevare (Mopti, Mopti).</t>
+          <t>On 5 March 2024, FAMA and Wagner forces arrested several students from Fulani community in the town of Sevare (Mopti, Mopti). ---- Around 15 August 2024 (month of), JNIM militants killed at least one adolescent Quranic school student (Talibe) in the village of Niakongo (Mopti, Mopti). ---- On 31 October 2024, JNIM militants abducted a coranic school teacher in Sevare (Mopti, Mopti) ---- On 9 November 2024, JNIM militants killed two adolescent Quranic school students (Talibes) in the village of Niakongo (Mopti, Mopti).</t>
         </is>
       </c>
       <c r="BK30" t="inlineStr">
         <is>
-          <t>09 November 2024 ---- 31 October 2024 ---- 15 August 2024 ---- 05 March 2024</t>
-        </is>
-      </c>
-      <c r="BL30" t="n">
+          <t>2024-03-05 ---- 2024-08-15 ---- 2024-10-31 ---- 2024-11-09</t>
+        </is>
+      </c>
+      <c r="BL30" t="inlineStr">
+        <is>
+          <t>Mopti</t>
+        </is>
+      </c>
+      <c r="BM30" t="n">
         <v>0.1495662714496761</v>
       </c>
     </row>
@@ -4694,7 +4764,8 @@
       <c r="BI31" t="inlineStr"/>
       <c r="BJ31" t="inlineStr"/>
       <c r="BK31" t="inlineStr"/>
-      <c r="BL31" t="n">
+      <c r="BL31" t="inlineStr"/>
+      <c r="BM31" t="n">
         <v>0.03256678600936381</v>
       </c>
     </row>
@@ -4798,16 +4869,16 @@
           <t>Mopti</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>Youwarou</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>0</v>
       </c>
       <c r="BA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB32" t="n">
         <v>2</v>
+      </c>
+      <c r="BB32" t="inlineStr">
+        <is>
+          <t>ML05</t>
+        </is>
       </c>
       <c r="BC32" t="inlineStr"/>
       <c r="BD32" t="inlineStr">
@@ -4834,15 +4905,20 @@
       <c r="BI32" t="inlineStr"/>
       <c r="BJ32" t="inlineStr">
         <is>
-          <t>On 14 January 2025, students from the public high school staged a peaceful demonstration in the town of Youwarou (Youwarou, Mopti). They protested against the transfer of a literature teacher to another town, at a time when the school is facing a teacher shortage. ---- Around 9 January 2025 (between 6 - 12 January), students from the public high school staged a peaceful demonstration in the town of Youwarou (Youwarou, Mopti). They protested against the lack of teachers in the school.</t>
+          <t>Around 9 January 2025 (between 6 - 12 January), students from the public high school staged a peaceful demonstration in the town of Youwarou (Youwarou, Mopti). They protested against the lack of teachers in the school. ---- On 14 January 2025, students from the public high school staged a peaceful demonstration in the town of Youwarou (Youwarou, Mopti). They protested against the transfer of a literature teacher to another town, at a time when the school is facing a teacher shortage.</t>
         </is>
       </c>
       <c r="BK32" t="inlineStr">
         <is>
-          <t>14 January 2025 ---- 09 January 2025</t>
-        </is>
-      </c>
-      <c r="BL32" t="n">
+          <t>2025-01-09 ---- 2025-01-14</t>
+        </is>
+      </c>
+      <c r="BL32" t="inlineStr">
+        <is>
+          <t>Youwarou</t>
+        </is>
+      </c>
+      <c r="BM32" t="n">
         <v>0.04480656990857911</v>
       </c>
     </row>
@@ -4946,16 +5022,16 @@
           <t>Tombouctou</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>Dire</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>0</v>
       </c>
       <c r="BA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB33" t="n">
         <v>1</v>
+      </c>
+      <c r="BB33" t="inlineStr">
+        <is>
+          <t>ML06</t>
+        </is>
       </c>
       <c r="BC33" t="inlineStr"/>
       <c r="BD33" t="inlineStr">
@@ -4987,10 +5063,15 @@
       </c>
       <c r="BK33" t="inlineStr">
         <is>
-          <t>22 April 2024</t>
-        </is>
-      </c>
-      <c r="BL33" t="n">
+          <t>2024-04-22</t>
+        </is>
+      </c>
+      <c r="BL33" t="inlineStr">
+        <is>
+          <t>Dire</t>
+        </is>
+      </c>
+      <c r="BM33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5156,31 +5237,31 @@
           <t>Tombouctou</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>Goundam</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>2</v>
       </c>
       <c r="BA34" t="n">
         <v>2</v>
       </c>
-      <c r="BB34" t="n">
-        <v>1</v>
+      <c r="BB34" t="inlineStr">
+        <is>
+          <t>ML06</t>
+        </is>
       </c>
       <c r="BC34" t="inlineStr"/>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>Violence against civilians</t>
+          <t>Violence against civilians ---- Violence against civilians</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>Attack ---- Abduction/forced disappearance</t>
         </is>
       </c>
       <c r="BF34" t="inlineStr">
         <is>
-          <t>Military Forces of Mali (2021-)</t>
+          <t>Military Forces of Mali (2021-) ---- JNIM: Group for Support of Islam and Muslims</t>
         </is>
       </c>
       <c r="BG34" t="inlineStr">
@@ -5190,25 +5271,30 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>Civilians (Mali)</t>
+          <t>Civilians (Mali) ---- Civilians (Mali)</t>
         </is>
       </c>
       <c r="BI34" t="inlineStr">
         <is>
-          <t>Teachers (Mali)</t>
+          <t>Teachers (Mali) ---- Muslim Group (Mali); Teachers (Mali)</t>
         </is>
       </c>
       <c r="BJ34" t="inlineStr">
         <is>
-          <t>On 4 February 2024, FAMa and Wagner forces killed two civilians including a school director and his son in the town of Essakane (Goundam, Tombouctou).</t>
+          <t>On 4 February 2024, FAMa and Wagner forces killed two civilians including a school director and his son in the town of Essakane (Goundam, Tombouctou). ---- On 21 July 2025, suspected JNIM militants abducted a coranic school teacher in the town of Douekire (Goundam, Tombouctou)</t>
         </is>
       </c>
       <c r="BK34" t="inlineStr">
         <is>
-          <t>04 February 2024</t>
-        </is>
-      </c>
-      <c r="BL34" t="n">
+          <t>2024-02-04 ---- 2025-07-21</t>
+        </is>
+      </c>
+      <c r="BL34" t="inlineStr">
+        <is>
+          <t>Goundam</t>
+        </is>
+      </c>
+      <c r="BM34" t="n">
         <v>0.02587424719323899</v>
       </c>
     </row>
@@ -5312,16 +5398,16 @@
           <t>Tombouctou</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>Gourma-Rharous</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>0</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB35" t="n">
         <v>2</v>
+      </c>
+      <c r="BB35" t="inlineStr">
+        <is>
+          <t>ML06</t>
+        </is>
       </c>
       <c r="BC35" t="inlineStr"/>
       <c r="BD35" t="inlineStr">
@@ -5348,15 +5434,20 @@
       <c r="BI35" t="inlineStr"/>
       <c r="BJ35" t="inlineStr">
         <is>
-          <t>On 29 April 2024, teachers renewed the work 72hours-stoppage in Gourma-Rharous (Gourma-Rharous, Tombouctou). They protested called for an enrolment team to arrive at the Gourma-Rharous Academy to enroll teachers. ---- On 24 April 2024, teachers renewed the work 72hours-stoppage in Gourma-Rharous (Gourma-Rharous, Tombouctou). The protesters called for an enrolment team to arrive at the Gourma-Rharous Academy to enroll teachers.</t>
+          <t>On 24 April 2024, teachers renewed the work 72hours-stoppage in Gourma-Rharous (Gourma-Rharous, Tombouctou). The protesters called for an enrolment team to arrive at the Gourma-Rharous Academy to enroll teachers. ---- On 29 April 2024, teachers renewed the work 72hours-stoppage in Gourma-Rharous (Gourma-Rharous, Tombouctou). They protested called for an enrolment team to arrive at the Gourma-Rharous Academy to enroll teachers.</t>
         </is>
       </c>
       <c r="BK35" t="inlineStr">
         <is>
-          <t>29 April 2024 ---- 24 April 2024</t>
-        </is>
-      </c>
-      <c r="BL35" t="n">
+          <t>2024-04-24 ---- 2024-04-29</t>
+        </is>
+      </c>
+      <c r="BL35" t="inlineStr">
+        <is>
+          <t>Gourma-Rharous</t>
+        </is>
+      </c>
+      <c r="BM35" t="n">
         <v>0.05394237753207973</v>
       </c>
     </row>
@@ -5526,16 +5617,16 @@
           <t>Tombouctou</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>Niafunke</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>2</v>
       </c>
       <c r="BA36" t="n">
         <v>2</v>
       </c>
-      <c r="BB36" t="n">
-        <v>2</v>
+      <c r="BB36" t="inlineStr">
+        <is>
+          <t>ML06</t>
+        </is>
       </c>
       <c r="BC36" t="inlineStr"/>
       <c r="BD36" t="inlineStr">
@@ -5545,7 +5636,7 @@
       </c>
       <c r="BE36" t="inlineStr">
         <is>
-          <t>Attack ---- Abduction/forced disappearance</t>
+          <t>Abduction/forced disappearance ---- Attack</t>
         </is>
       </c>
       <c r="BF36" t="inlineStr">
@@ -5566,15 +5657,20 @@
       </c>
       <c r="BJ36" t="inlineStr">
         <is>
-          <t>On 18 August 2024, JNIM militants killed two school principals in the village of Arabebe (Niafunke, Tombouctou). The lifeless bodies of the school principals were found near the village health center. ---- On 15 August 2024, JNIM abducted two school principals near the village of Arabebe (Niafunke, Tombouctou).</t>
+          <t>On 15 August 2024, JNIM abducted two school principals near the village of Arabebe (Niafunke, Tombouctou). ---- On 18 August 2024, JNIM militants killed two school principals in the village of Arabebe (Niafunke, Tombouctou). The lifeless bodies of the school principals were found near the village health center.</t>
         </is>
       </c>
       <c r="BK36" t="inlineStr">
         <is>
-          <t>18 August 2024 ---- 15 August 2024</t>
-        </is>
-      </c>
-      <c r="BL36" t="n">
+          <t>2024-08-15 ---- 2024-08-18</t>
+        </is>
+      </c>
+      <c r="BL36" t="inlineStr">
+        <is>
+          <t>Niafunke</t>
+        </is>
+      </c>
+      <c r="BM36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5686,7 +5782,8 @@
       <c r="BI37" t="inlineStr"/>
       <c r="BJ37" t="inlineStr"/>
       <c r="BK37" t="inlineStr"/>
-      <c r="BL37" t="n">
+      <c r="BL37" t="inlineStr"/>
+      <c r="BM37" t="n">
         <v>0.09848373541770739</v>
       </c>
     </row>
@@ -5785,20 +5882,65 @@
       <c r="AV38" t="inlineStr"/>
       <c r="AW38" t="inlineStr"/>
       <c r="AX38" t="inlineStr"/>
-      <c r="AY38" t="inlineStr"/>
-      <c r="AZ38" t="inlineStr"/>
-      <c r="BA38" t="inlineStr"/>
-      <c r="BB38" t="inlineStr"/>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Gao</t>
+        </is>
+      </c>
+      <c r="AZ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB38" t="inlineStr">
+        <is>
+          <t>ML07</t>
+        </is>
+      </c>
       <c r="BC38" t="inlineStr"/>
-      <c r="BD38" t="inlineStr"/>
-      <c r="BE38" t="inlineStr"/>
-      <c r="BF38" t="inlineStr"/>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>Violence against civilians</t>
+        </is>
+      </c>
+      <c r="BE38" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="BF38" t="inlineStr">
+        <is>
+          <t>Unidentified Armed Group (Mali)</t>
+        </is>
+      </c>
       <c r="BG38" t="inlineStr"/>
-      <c r="BH38" t="inlineStr"/>
-      <c r="BI38" t="inlineStr"/>
-      <c r="BJ38" t="inlineStr"/>
-      <c r="BK38" t="inlineStr"/>
-      <c r="BL38" t="n">
+      <c r="BH38" t="inlineStr">
+        <is>
+          <t>Civilians (Mali)</t>
+        </is>
+      </c>
+      <c r="BI38" t="inlineStr">
+        <is>
+          <t>Women (Mali)</t>
+        </is>
+      </c>
+      <c r="BJ38" t="inlineStr">
+        <is>
+          <t>On 27 June 2025, unidentified armed men went to the home of the principal of the local school in the village of Tabango (Ansongo, Gao). The principal was not at home and the gunmen beat his wife (no further details).</t>
+        </is>
+      </c>
+      <c r="BK38" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="BL38" t="inlineStr">
+        <is>
+          <t>Ansongo</t>
+        </is>
+      </c>
+      <c r="BM38" t="n">
         <v>0.06684593430885725</v>
       </c>
     </row>
@@ -5902,16 +6044,16 @@
           <t>Gao</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>Bourem</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>3</v>
       </c>
       <c r="BA39" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB39" t="n">
         <v>1</v>
+      </c>
+      <c r="BB39" t="inlineStr">
+        <is>
+          <t>ML07</t>
+        </is>
       </c>
       <c r="BC39" t="inlineStr"/>
       <c r="BD39" t="inlineStr">
@@ -5947,10 +6089,15 @@
       </c>
       <c r="BK39" t="inlineStr">
         <is>
-          <t>27 May 2024</t>
-        </is>
-      </c>
-      <c r="BL39" t="n">
+          <t>2024-05-27</t>
+        </is>
+      </c>
+      <c r="BL39" t="inlineStr">
+        <is>
+          <t>Bourem</t>
+        </is>
+      </c>
+      <c r="BM39" t="n">
         <v>0.07333842627960276</v>
       </c>
     </row>
@@ -6054,55 +6201,60 @@
           <t>Gao</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>Gao</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>1</v>
       </c>
       <c r="BA40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB40" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="BB40" t="inlineStr">
+        <is>
+          <t>ML07</t>
+        </is>
       </c>
       <c r="BC40" t="inlineStr"/>
       <c r="BD40" t="inlineStr">
         <is>
-          <t>Violence against civilians</t>
+          <t>Violence against civilians ---- Violence against civilians</t>
         </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
-          <t>Abduction/forced disappearance</t>
+          <t>Abduction/forced disappearance ---- Attack</t>
         </is>
       </c>
       <c r="BF40" t="inlineStr">
         <is>
-          <t>Unidentified Armed Group (Mali)</t>
+          <t>Unidentified Armed Group (Mali) ---- Unidentified Armed Group (Mali)</t>
         </is>
       </c>
       <c r="BG40" t="inlineStr"/>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>Civilians (Mali)</t>
+          <t>Civilians (Mali) ---- Civilians (Mali)</t>
         </is>
       </c>
       <c r="BI40" t="inlineStr">
         <is>
-          <t>Teachers (Mali)</t>
+          <t>Teachers (Mali) ---- Teachers (Mali)</t>
         </is>
       </c>
       <c r="BJ40" t="inlineStr">
         <is>
-          <t>On 26 April 2025, unidentified gunmen abducted a teacher and a resident in the village of Kobe (Gao, Gao). The gunmen claimed 3,000,000 CFA for their release. On 28 April 2025, they were released in exchange of payment (amount unknown).</t>
+          <t>On 26 April 2025, unidentified gunmen abducted a teacher and a resident in the village of Kobe (Gao, Gao). The gunmen claimed 3,000,000 CFA for their release. On 28 April 2025, they were released in exchange of payment (amount unknown). ---- On 5 June 2025, unidentified gunmen shot dead the principal of a secondary school in the village of Magnadoue (Gao, Gao). Seriously wounded in Magnadoue, he was taken to hospital in Gao, where he succumbed to his injuries.</t>
         </is>
       </c>
       <c r="BK40" t="inlineStr">
         <is>
-          <t>26 April 2025</t>
-        </is>
-      </c>
-      <c r="BL40" t="n">
+          <t>2025-04-26 ---- 2025-06-05</t>
+        </is>
+      </c>
+      <c r="BL40" t="inlineStr">
+        <is>
+          <t>Gao</t>
+        </is>
+      </c>
+      <c r="BM40" t="n">
         <v>0.1273930826270106</v>
       </c>
     </row>
@@ -6214,7 +6366,8 @@
       <c r="BI41" t="inlineStr"/>
       <c r="BJ41" t="inlineStr"/>
       <c r="BK41" t="inlineStr"/>
-      <c r="BL41" t="n">
+      <c r="BL41" t="inlineStr"/>
+      <c r="BM41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6318,16 +6471,16 @@
           <t>Kidal</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>Kidal</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>2</v>
       </c>
       <c r="BA42" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB42" t="n">
         <v>1</v>
+      </c>
+      <c r="BB42" t="inlineStr">
+        <is>
+          <t>ML08</t>
+        </is>
       </c>
       <c r="BC42" t="inlineStr"/>
       <c r="BD42" t="inlineStr">
@@ -6367,10 +6520,15 @@
       </c>
       <c r="BK42" t="inlineStr">
         <is>
-          <t>22 April 2024</t>
-        </is>
-      </c>
-      <c r="BL42" t="n">
+          <t>2024-04-22</t>
+        </is>
+      </c>
+      <c r="BL42" t="inlineStr">
+        <is>
+          <t>Kidal</t>
+        </is>
+      </c>
+      <c r="BM42" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6474,26 +6632,26 @@
           <t>Kidal</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>Tessalit</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>2</v>
       </c>
       <c r="BA43" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB43" t="n">
         <v>4</v>
+      </c>
+      <c r="BB43" t="inlineStr">
+        <is>
+          <t>ML08</t>
+        </is>
       </c>
       <c r="BC43" t="inlineStr"/>
       <c r="BD43" t="inlineStr">
         <is>
-          <t>Violence against civilians ---- Strategic developments ---- Violence against civilians ---- Strategic developments</t>
+          <t>Strategic developments ---- Violence against civilians ---- Strategic developments ---- Violence against civilians</t>
         </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
-          <t>Attack ---- Looting/property destruction ---- Attack ---- Arrests</t>
+          <t>Arrests ---- Attack ---- Looting/property destruction ---- Attack</t>
         </is>
       </c>
       <c r="BF43" t="inlineStr">
@@ -6513,20 +6671,25 @@
       </c>
       <c r="BI43" t="inlineStr">
         <is>
-          <t>Prisoners (Mali); Teachers (Mali) ---- Labor Group (Mali) ---- Teachers (Mali) ---- Teachers (Mali)</t>
+          <t>Teachers (Mali) ---- Teachers (Mali) ---- Labor Group (Mali) ---- Prisoners (Mali); Teachers (Mali)</t>
         </is>
       </c>
       <c r="BJ43" t="inlineStr">
         <is>
-          <t>Around 28 January 2025 (between 24 January - 1 February), FAMa and Wagner forces killed a teacher and her body was found near the village of Assamalmal (Tessalit, Kidal). He was arrested on 25 January 2025 in the village of Talabit. ---- Looting: On 25 January 2025, a FAMa and Wagner patrol looted shops, burned houses, arrested two civilians, including a teacher and a pharmacy manager, and damaged an Internet station in the village of Intechaq (Tessalit, Kidal). ---- On 20 January 2025, FAMa and Wagner forces killed a teacher in the town of Aguelhok (Tessalit, Kidal). He was arrested on 18 January 2025 in the area of Gossi (Gourma-Rharous, Tombouctou). ---- On 24 April 2024, FAMa and Wagner arrested a teacher in the town of Tessalit (Tessalit, Kidal).</t>
+          <t>On 24 April 2024, FAMa and Wagner arrested a teacher in the town of Tessalit (Tessalit, Kidal). ---- On 20 January 2025, FAMa and Wagner forces killed a teacher in the town of Aguelhok (Tessalit, Kidal). He was arrested on 18 January 2025 in the area of Gossi (Gourma-Rharous, Tombouctou). ---- Looting: On 25 January 2025, a FAMa and Wagner patrol looted shops, burned houses, arrested two civilians, including a teacher and a pharmacy manager, and damaged an Internet station in the village of Intechaq (Tessalit, Kidal). ---- Around 28 January 2025 (between 24 January - 1 February), FAMa and Wagner forces killed a teacher and her body was found near the village of Assamalmal (Tessalit, Kidal). He was arrested on 25 January 2025 in the village of Talabit.</t>
         </is>
       </c>
       <c r="BK43" t="inlineStr">
         <is>
-          <t>28 January 2025 ---- 25 January 2025 ---- 20 January 2025 ---- 24 April 2024</t>
-        </is>
-      </c>
-      <c r="BL43" t="n">
+          <t>2024-04-24 ---- 2025-01-20 ---- 2025-01-25 ---- 2025-01-28</t>
+        </is>
+      </c>
+      <c r="BL43" t="inlineStr">
+        <is>
+          <t>Tessalit</t>
+        </is>
+      </c>
+      <c r="BM43" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6692,16 +6855,16 @@
           <t>Kidal</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>Tin-Essako</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>0</v>
       </c>
       <c r="BA44" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB44" t="n">
         <v>2</v>
+      </c>
+      <c r="BB44" t="inlineStr">
+        <is>
+          <t>ML08</t>
+        </is>
       </c>
       <c r="BC44" t="inlineStr"/>
       <c r="BD44" t="inlineStr">
@@ -6728,15 +6891,20 @@
       <c r="BI44" t="inlineStr"/>
       <c r="BJ44" t="inlineStr">
         <is>
-          <t>On 1 October 2024, the Malian air force carried out a drone strike on a school in the village of Inakarot (Tin Essako, Kidal). Casualties unknown. ---- On 19 June 2024, the Malian air force carried out an airstrike against a vehicle in the village of Tin Essako (Tin Essako, Kidal). The vehicle had broken down and was parked near a school. A young boy was injured.</t>
+          <t>On 19 June 2024, the Malian air force carried out an airstrike against a vehicle in the village of Tin Essako (Tin Essako, Kidal). The vehicle had broken down and was parked near a school. A young boy was injured. ---- On 1 October 2024, the Malian air force carried out a drone strike on a school in the village of Inakarot (Tin Essako, Kidal). Casualties unknown.</t>
         </is>
       </c>
       <c r="BK44" t="inlineStr">
         <is>
-          <t>01 October 2024 ---- 19 June 2024</t>
-        </is>
-      </c>
-      <c r="BL44" t="n">
+          <t>2024-06-19 ---- 2024-10-01</t>
+        </is>
+      </c>
+      <c r="BL44" t="inlineStr">
+        <is>
+          <t>Tin-Essako</t>
+        </is>
+      </c>
+      <c r="BM44" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6840,36 +7008,36 @@
           <t>Bamako</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>Bamako</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>1</v>
       </c>
       <c r="BA45" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB45" t="n">
         <v>2</v>
+      </c>
+      <c r="BB45" t="inlineStr">
+        <is>
+          <t>ML09</t>
+        </is>
       </c>
       <c r="BC45" t="inlineStr"/>
       <c r="BD45" t="inlineStr">
         <is>
-          <t>Protests ---- Riots</t>
+          <t>Riots ---- Protests</t>
         </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
-          <t>Peaceful protest ---- Mob violence</t>
+          <t>Mob violence ---- Peaceful protest</t>
         </is>
       </c>
       <c r="BF45" t="inlineStr">
         <is>
-          <t>Protesters (Mali) ---- Rioters (Mali)</t>
+          <t>Rioters (Mali) ---- Protesters (Mali)</t>
         </is>
       </c>
       <c r="BG45" t="inlineStr">
         <is>
-          <t>Students (Mali) ---- AEEM: Association of Students and Pupils in Mali; Students (Mali)</t>
+          <t>AEEM: Association of Students and Pupils in Mali; Students (Mali) ---- Students (Mali)</t>
         </is>
       </c>
       <c r="BH45" t="inlineStr">
@@ -6884,15 +7052,20 @@
       </c>
       <c r="BJ45" t="inlineStr">
         <is>
-          <t>On 28 May 2024, a number of students demonstrated peacefully in Kabala university campus in the city of Bamako (Bamako, Bamako) to denounce the water shortage in the campus. ---- On 27 February 2024, two rival camps of the AEEM student organization clashed with stabbing weapons at the Badalabougou University in the city of Bamako (Bamako, Bamako). One student was killed. Following the incident, the Minister of Higher Education and Scientific Research suspended the activities of the coordinating office of the AEEM at the university until further notice.</t>
+          <t>On 27 February 2024, two rival camps of the AEEM student organization clashed with stabbing weapons at the Badalabougou University in the city of Bamako (Bamako, Bamako). One student was killed. Following the incident, the Minister of Higher Education and Scientific Research suspended the activities of the coordinating office of the AEEM at the university until further notice. ---- On 28 May 2024, a number of students demonstrated peacefully in Kabala university campus in the city of Bamako (Bamako, Bamako) to denounce the water shortage in the campus.</t>
         </is>
       </c>
       <c r="BK45" t="inlineStr">
         <is>
-          <t>28 May 2024 ---- 27 February 2024</t>
-        </is>
-      </c>
-      <c r="BL45" t="n">
+          <t>2024-02-27 ---- 2024-05-28</t>
+        </is>
+      </c>
+      <c r="BL45" t="inlineStr">
+        <is>
+          <t>Bamako</t>
+        </is>
+      </c>
+      <c r="BM45" t="n">
         <v>0.1605693852289919</v>
       </c>
     </row>
@@ -6996,16 +7169,16 @@
           <t>Menaka</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>Menaka</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>12</v>
       </c>
       <c r="BA46" t="n">
-        <v>12</v>
-      </c>
-      <c r="BB46" t="n">
         <v>1</v>
+      </c>
+      <c r="BB46" t="inlineStr">
+        <is>
+          <t>ML10</t>
+        </is>
       </c>
       <c r="BC46" t="inlineStr"/>
       <c r="BD46" t="inlineStr">
@@ -7041,10 +7214,15 @@
       </c>
       <c r="BK46" t="inlineStr">
         <is>
-          <t>02 January 2024</t>
-        </is>
-      </c>
-      <c r="BL46" t="n">
+          <t>2024-01-02</t>
+        </is>
+      </c>
+      <c r="BL46" t="inlineStr">
+        <is>
+          <t>Menaka</t>
+        </is>
+      </c>
+      <c r="BM46" t="n">
         <v>0.5734549545929438</v>
       </c>
     </row>
@@ -7054,10 +7232,10 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C9824523CAB29F4DA646F20BAFE41B4C" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9c972c102b01d47663811fb2ebdbd1e4">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b5940141-1bc9-4c17-b1bc-e50f6b2083d6" xmlns:ns3="14cbb838-50ff-4dab-9c3f-cddf75f03c13" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="bd0e8b72e466adcc572d3af37c1ebe05" ns2:_="" ns3:_="">
-    <xsd:import namespace="b5940141-1bc9-4c17-b1bc-e50f6b2083d6"/>
-    <xsd:import namespace="14cbb838-50ff-4dab-9c3f-cddf75f03c13"/>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DE51FB2AFBB2DD429D3D11FE759FFC43" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1354c8e90e28409d311bbba5db8dc335">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f4877444-78fa-4cfa-bafc-d6c64fafc061" xmlns:ns3="d0fa6634-326e-4532-91a2-52bea7ac9212" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dbb4473bd7833dc3543803a005841490" ns2:_="" ns3:_="">
+    <xsd:import namespace="f4877444-78fa-4cfa-bafc-d6c64fafc061"/>
+    <xsd:import namespace="d0fa6634-326e-4532-91a2-52bea7ac9212"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
@@ -7069,13 +7247,15 @@
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
                 <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
                 <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
@@ -7084,7 +7264,7 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="b5940141-1bc9-4c17-b1bc-e50f6b2083d6" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f4877444-78fa-4cfa-bafc-d6c64fafc061" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
@@ -7102,52 +7282,57 @@
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="14" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4d06f0b5-5743-41f2-90d3-b12c8ffc7f36" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="MediaServiceDateTaken" ma:index="13" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="16" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="18" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4d06f0b5-5743-41f2-90d3-b12c8ffc7f36" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
         </xsd:sequence>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+    <xsd:element name="MediaServiceOCR" ma:index="20" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+    <xsd:element name="MediaServiceSearchProperties" ma:index="21" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="22" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="18" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="19" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceBillingMetadata" ma:index="21" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="23" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="14cbb838-50ff-4dab-9c3f-cddf75f03c13" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="d0fa6634-326e-4532-91a2-52bea7ac9212" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <xsd:element name="SharedWithUsers" ma:index="11" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
@@ -7175,6 +7360,17 @@
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="19" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{d6bd4e25-e667-4943-8e38-5db701f530ee}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="d0fa6634-326e-4532-91a2-52bea7ac9212">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -7288,21 +7484,22 @@
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b5940141-1bc9-4c17-b1bc-e50f6b2083d6">
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4877444-78fa-4cfa-bafc-d6c64fafc061">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="d0fa6634-326e-4532-91a2-52bea7ac9212" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8455B03F-33DA-4712-88A8-77C99CCAED67}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15F59B28-F267-4FCE-AAE7-391593FB63B8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66008F2B-D050-4D52-89A7-0F198BADA5ED}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B859731-317D-483E-AECF-FA22B4D5CA40}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7DA9C1C-6D54-4C5D-89A3-E0B4858B557C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F342E2B-043C-442B-90E3-145B24DB004E}"/>
 </file>
--- a/context_DB/MLI_context_db.xlsx
+++ b/context_DB/MLI_context_db.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM46"/>
+  <dimension ref="A1:BM48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2284,71 +2284,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ML0301</t>
+          <t>ML0207</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>ML0306</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>ML0101;ML0105;ML0301;ML0302;ML0306</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="I14" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="M14" t="n">
-        <v>77.27000000000001</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
@@ -2376,20 +2336,68 @@
       <c r="AV14" t="inlineStr"/>
       <c r="AW14" t="inlineStr"/>
       <c r="AX14" t="inlineStr"/>
-      <c r="AY14" t="inlineStr"/>
-      <c r="AZ14" t="inlineStr"/>
-      <c r="BA14" t="inlineStr"/>
-      <c r="BB14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Koulikoro</t>
+        </is>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>ML02</t>
+        </is>
+      </c>
       <c r="BC14" t="inlineStr"/>
-      <c r="BD14" t="inlineStr"/>
-      <c r="BE14" t="inlineStr"/>
-      <c r="BF14" t="inlineStr"/>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
-      <c r="BI14" t="inlineStr"/>
-      <c r="BJ14" t="inlineStr"/>
-      <c r="BK14" t="inlineStr"/>
-      <c r="BL14" t="inlineStr"/>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>Protests ---- Violence against civilians</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>Peaceful protest ---- Attack</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>Protesters (Mali) ---- JNIM: Group for Support of Islam and Muslims</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>Teachers (Mali)</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>Civilians (Mali)</t>
+        </is>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>Muslim Group (Mali); Students (Mali)</t>
+        </is>
+      </c>
+      <c r="BJ14" t="inlineStr">
+        <is>
+          <t>On 4 November 2024, a number of teachers in communal schools staged a demonstration in the town of Nara (Nara, Koulikoro) to demand four months of unpaid salaries. ---- On 4 March 2025, JNIM militants attacked three coranic school students from their teacher's garden in Mourdiah (Nara, Koulikoro). 1 student was killed and two managed to escape.</t>
+        </is>
+      </c>
+      <c r="BK14" t="inlineStr">
+        <is>
+          <t>2024-11-04 ---- 2025-03-04</t>
+        </is>
+      </c>
+      <c r="BL14" t="inlineStr">
+        <is>
+          <t>Nara</t>
+        </is>
+      </c>
       <c r="BM14" t="n">
         <v>0</v>
       </c>
@@ -2397,7 +2405,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ML0304</t>
+          <t>ML0301</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -2406,31 +2414,31 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ML0203</t>
+          <t>ML0306</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>ML0102;ML0103;ML0106;ML0203;ML0304;ML0802</t>
+          <t>ML0101;ML0105;ML0301;ML0302;ML0306</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>46.6</v>
+        <v>51.5</v>
       </c>
       <c r="I15" t="n">
-        <v>43.6</v>
+        <v>48.5</v>
       </c>
       <c r="J15" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>53.4</v>
+        <v>48.5</v>
       </c>
       <c r="M15" t="n">
-        <v>75.36</v>
+        <v>77.27000000000001</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2439,19 +2447,19 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.78</v>
+        <v>0.38</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.49</v>
+        <v>2.65</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.87</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>22.26</v>
+        <v>0.76</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -2460,7 +2468,7 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr"/>
@@ -2504,13 +2512,13 @@
       <c r="BK15" t="inlineStr"/>
       <c r="BL15" t="inlineStr"/>
       <c r="BM15" t="n">
-        <v>0.18997668997669</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ML0305</t>
+          <t>ML0302</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -2519,62 +2527,30 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ML0204</t>
+          <t>ML0105</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>ML0201;ML0204;ML0206;ML0305;ML0401;ML0403;ML0404;ML0406;ML0407;ML0505;ML0601;ML0605;ML0701;ML0702;ML0703;ML1001</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>61.1</v>
-      </c>
-      <c r="I16" t="n">
-        <v>33.7</v>
-      </c>
-      <c r="J16" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L16" t="n">
-        <v>38.9</v>
-      </c>
-      <c r="M16" t="n">
-        <v>26.32</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>4.74</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0.53</v>
-      </c>
+          <t>ML0101;ML0105;ML0301;ML0302;ML0306</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
@@ -2611,7 +2587,7 @@
         <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
@@ -2621,17 +2597,17 @@
       <c r="BC16" t="inlineStr"/>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>Battles ---- Protests</t>
+          <t>Protests</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>Armed clash ---- Peaceful protest</t>
+          <t>Peaceful protest</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>JNIM: Group for Support of Islam and Muslims ---- Protesters (Mali)</t>
+          <t>Protesters (Mali)</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
@@ -2639,25 +2615,21 @@
           <t>Teachers (Mali)</t>
         </is>
       </c>
-      <c r="BH16" t="inlineStr">
-        <is>
-          <t>Police Forces of Mali (2021-) Gendarmerie</t>
-        </is>
-      </c>
+      <c r="BH16" t="inlineStr"/>
       <c r="BI16" t="inlineStr"/>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>On 13 February 2025, JNIM militants attacked a convoy of the Minister of Higher Education escorted by gendarmes between Darabougou and Niena (Sikasso, Sikasso), coded to Darabougou. The militants fired a rocket, followed by AK rifles fire. The attack was repulsed, and four gendarmes were injured. The convoy passed the incident place and reached the town of Niena. ---- On 3 March 2025, teachers staged a demonstration in the town of Niena (Sikasso, Sikasso) to demand the release of a member of the teachers' union arrested by the local Police.</t>
+          <t>On 15 April 2024, teachers observed a work stoppage in the commune of Kadiolo (Kadiolo, Sikasso). They protested against the transfer of a teacher from Kadiolo to a village of the commune. The protester said that the teacher is suffering from an illness that prevents him from moving away from the town of Kadiolo.</t>
         </is>
       </c>
       <c r="BK16" t="inlineStr">
         <is>
-          <t>2025-02-13 ---- 2025-03-03</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>Sikasso</t>
+          <t>Kadiolo</t>
         </is>
       </c>
       <c r="BM16" t="n">
@@ -2667,7 +2639,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ML0307</t>
+          <t>ML0304</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -2676,31 +2648,31 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ML0502</t>
+          <t>ML0203</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>ML0307;ML0502;ML0804</t>
+          <t>ML0102;ML0103;ML0106;ML0203;ML0304;ML0802</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>47.4</v>
+        <v>46.6</v>
       </c>
       <c r="I17" t="n">
-        <v>44.6</v>
+        <v>43.6</v>
       </c>
       <c r="J17" t="n">
-        <v>8</v>
+        <v>8.9</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="L17" t="n">
-        <v>52.6</v>
+        <v>53.4</v>
       </c>
       <c r="M17" t="n">
-        <v>44.55</v>
+        <v>75.36</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2709,19 +2681,19 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0.64</v>
+        <v>1.78</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.41</v>
+        <v>3.49</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.96</v>
+        <v>0.87</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>22.26</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -2730,94 +2702,32 @@
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>4</v>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>2025-01-07 ---- 2025-01-07 ---- 2025-01-07 ---- 2025-01-07</t>
-        </is>
-      </c>
-      <c r="AP17" t="inlineStr">
-        <is>
-          <t>As reported in January 2025: An education facility was ordered to close by armed men. Teachers were threatened not to work until further notice. ---- As reported in January 2025: An education facility was ordered to close by armed men. Teachers were threatened not to work until further notice. ---- As reported in January 2025: An education facility was ordered to close by armed men. Teachers were threatened not to work until further notice. ---- As reported in January 2025: An education facility was ordered to close by armed men. Teachers were threatened not to work until further notice.</t>
-        </is>
-      </c>
-      <c r="AQ17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Education Building  ---- Education Building  ---- Education Building  ---- Education Building </t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>NSA ---- NSA ---- NSA ---- NSA</t>
-        </is>
-      </c>
-      <c r="AS17" t="inlineStr">
-        <is>
-          <t>Unidentified Armed Actor ---- Unidentified Armed Actor ---- Unidentified Armed Actor ---- Unidentified Armed Actor</t>
-        </is>
-      </c>
-      <c r="AT17" t="inlineStr">
-        <is>
-          <t>Firearms ---- Firearms ---- Firearms ---- Firearms</t>
-        </is>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>School: No Further Details ---- School: No Further Details ---- School: No Further Details ---- School: No Further Details</t>
-        </is>
-      </c>
+        <v>4.55</v>
+      </c>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr"/>
+      <c r="AO17" t="inlineStr"/>
+      <c r="AP17" t="inlineStr"/>
+      <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="inlineStr"/>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AU17" t="inlineStr"/>
       <c r="AV17" t="inlineStr"/>
       <c r="AW17" t="inlineStr"/>
       <c r="AX17" t="inlineStr"/>
@@ -2836,13 +2746,13 @@
       <c r="BK17" t="inlineStr"/>
       <c r="BL17" t="inlineStr"/>
       <c r="BM17" t="n">
-        <v>0</v>
+        <v>0.18997668997669</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ML0401</t>
+          <t>ML0305</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -2860,22 +2770,22 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>48.5</v>
+        <v>61.1</v>
       </c>
       <c r="I18" t="n">
-        <v>49.2</v>
+        <v>33.7</v>
       </c>
       <c r="J18" t="n">
-        <v>1.7</v>
+        <v>4.7</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="L18" t="n">
-        <v>51.5</v>
+        <v>38.9</v>
       </c>
       <c r="M18" t="n">
-        <v>126.49</v>
+        <v>26.32</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2887,7 +2797,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.68</v>
+        <v>4.74</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2905,7 +2815,7 @@
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
@@ -2934,28 +2844,72 @@
       <c r="AV18" t="inlineStr"/>
       <c r="AW18" t="inlineStr"/>
       <c r="AX18" t="inlineStr"/>
-      <c r="AY18" t="inlineStr"/>
-      <c r="AZ18" t="inlineStr"/>
-      <c r="BA18" t="inlineStr"/>
-      <c r="BB18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Sikasso</t>
+        </is>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>ML03</t>
+        </is>
+      </c>
       <c r="BC18" t="inlineStr"/>
-      <c r="BD18" t="inlineStr"/>
-      <c r="BE18" t="inlineStr"/>
-      <c r="BF18" t="inlineStr"/>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>Battles ---- Protests</t>
+        </is>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>Armed clash ---- Peaceful protest</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>JNIM: Group for Support of Islam and Muslims ---- Protesters (Mali)</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>Teachers (Mali)</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>Police Forces of Mali (2021-) Gendarmerie</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr"/>
-      <c r="BJ18" t="inlineStr"/>
-      <c r="BK18" t="inlineStr"/>
-      <c r="BL18" t="inlineStr"/>
+      <c r="BJ18" t="inlineStr">
+        <is>
+          <t>On 13 February 2025, JNIM militants attacked a convoy of the Minister of Higher Education escorted by gendarmes between Darabougou and Niena (Sikasso, Sikasso), coded to Darabougou. The militants fired a rocket, followed by AK rifles fire. The attack was repulsed, and four gendarmes were injured. The convoy passed the incident place and reached the town of Niena. ---- On 3 March 2025, teachers staged a demonstration in the town of Niena (Sikasso, Sikasso) to demand the release of a member of the teachers' union arrested by the local Police.</t>
+        </is>
+      </c>
+      <c r="BK18" t="inlineStr">
+        <is>
+          <t>2025-02-13 ---- 2025-03-03</t>
+        </is>
+      </c>
+      <c r="BL18" t="inlineStr">
+        <is>
+          <t>Sikasso</t>
+        </is>
+      </c>
       <c r="BM18" t="n">
-        <v>0.001673271686481726</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ML0402</t>
+          <t>ML0307</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -2964,31 +2918,31 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ML0402</t>
+          <t>ML0502</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>ML0402</t>
+          <t>ML0307;ML0502;ML0804</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>53.2</v>
+        <v>47.4</v>
       </c>
       <c r="I19" t="n">
-        <v>45.7</v>
+        <v>44.6</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>46.8</v>
+        <v>52.6</v>
       </c>
       <c r="M19" t="n">
-        <v>118.58</v>
+        <v>44.55</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2997,16 +2951,16 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.49</v>
+        <v>6.41</v>
       </c>
       <c r="R19" t="n">
-        <v>0.49</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -3018,32 +2972,94 @@
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>7.18</v>
-      </c>
-      <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
-      <c r="AA19" t="inlineStr"/>
-      <c r="AB19" t="inlineStr"/>
-      <c r="AC19" t="inlineStr"/>
-      <c r="AD19" t="inlineStr"/>
-      <c r="AE19" t="inlineStr"/>
-      <c r="AF19" t="inlineStr"/>
-      <c r="AG19" t="inlineStr"/>
-      <c r="AH19" t="inlineStr"/>
-      <c r="AI19" t="inlineStr"/>
-      <c r="AJ19" t="inlineStr"/>
-      <c r="AK19" t="inlineStr"/>
-      <c r="AL19" t="inlineStr"/>
-      <c r="AM19" t="inlineStr"/>
-      <c r="AN19" t="inlineStr"/>
-      <c r="AO19" t="inlineStr"/>
-      <c r="AP19" t="inlineStr"/>
-      <c r="AQ19" t="inlineStr"/>
-      <c r="AR19" t="inlineStr"/>
-      <c r="AS19" t="inlineStr"/>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AU19" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>2025-01-07 ---- 2025-01-07 ---- 2025-01-07 ---- 2025-01-07</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>As reported in January 2025: An education facility was ordered to close by armed men. Teachers were threatened not to work until further notice. ---- As reported in January 2025: An education facility was ordered to close by armed men. Teachers were threatened not to work until further notice. ---- As reported in January 2025: An education facility was ordered to close by armed men. Teachers were threatened not to work until further notice. ---- As reported in January 2025: An education facility was ordered to close by armed men. Teachers were threatened not to work until further notice.</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Education Building  ---- Education Building  ---- Education Building  ---- Education Building </t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>NSA ---- NSA ---- NSA ---- NSA</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>Unidentified Armed Actor ---- Unidentified Armed Actor ---- Unidentified Armed Actor ---- Unidentified Armed Actor</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>Firearms ---- Firearms ---- Firearms ---- Firearms</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>School: No Further Details ---- School: No Further Details ---- School: No Further Details ---- School: No Further Details</t>
+        </is>
+      </c>
       <c r="AV19" t="inlineStr"/>
       <c r="AW19" t="inlineStr"/>
       <c r="AX19" t="inlineStr"/>
@@ -3062,13 +3078,13 @@
       <c r="BK19" t="inlineStr"/>
       <c r="BL19" t="inlineStr"/>
       <c r="BM19" t="n">
-        <v>0.01949693019608941</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ML0403</t>
+          <t>ML0401</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -3077,7 +3093,7 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ML0407</t>
+          <t>ML0204</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3086,22 +3102,22 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>38.4</v>
+        <v>48.5</v>
       </c>
       <c r="I20" t="n">
-        <v>56</v>
+        <v>49.2</v>
       </c>
       <c r="J20" t="n">
-        <v>4.9</v>
+        <v>1.7</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="L20" t="n">
-        <v>61.6</v>
+        <v>51.5</v>
       </c>
       <c r="M20" t="n">
-        <v>123.03</v>
+        <v>126.49</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -3110,16 +3126,16 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0.41</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.449999999999999</v>
+        <v>1.68</v>
       </c>
       <c r="R20" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.47</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -3128,170 +3144,60 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>0.9399999999999999</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>7.96</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>2024-01-06 ---- 2024-01-03</t>
-        </is>
-      </c>
-      <c r="AP20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">January 2024: JNIM militants abducted two educators. They were released 3 days later. ---- January 2024: Two educators kidnapped by JNIM militants and the village burned. Both educators were released on 6 days later. </t>
-        </is>
-      </c>
-      <c r="AQ20" t="inlineStr">
-        <is>
-          <t>Unspecified Location ---- Unspecified Location</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>NSA ---- NSA</t>
-        </is>
-      </c>
-      <c r="AS20" t="inlineStr">
-        <is>
-          <t>Jama'at Nasr al-Islam wal Muslimin ---- Jama'at Nasr al-Islam wal Muslimin</t>
-        </is>
-      </c>
-      <c r="AT20" t="inlineStr">
-        <is>
-          <t>Firearms ---- Firearms</t>
-        </is>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>Not Applicable ---- Not Applicable</t>
-        </is>
-      </c>
-      <c r="AV20" t="inlineStr">
-        <is>
-          <t>Freed ---- Freed</t>
-        </is>
-      </c>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr"/>
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr"/>
+      <c r="AL20" t="inlineStr"/>
+      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="inlineStr"/>
+      <c r="AO20" t="inlineStr"/>
+      <c r="AP20" t="inlineStr"/>
+      <c r="AQ20" t="inlineStr"/>
+      <c r="AR20" t="inlineStr"/>
+      <c r="AS20" t="inlineStr"/>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AU20" t="inlineStr"/>
+      <c r="AV20" t="inlineStr"/>
       <c r="AW20" t="inlineStr"/>
       <c r="AX20" t="inlineStr"/>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>Segou</t>
-        </is>
-      </c>
-      <c r="AZ20" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB20" t="inlineStr">
-        <is>
-          <t>ML04</t>
-        </is>
-      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr"/>
+      <c r="BA20" t="inlineStr"/>
+      <c r="BB20" t="inlineStr"/>
       <c r="BC20" t="inlineStr"/>
-      <c r="BD20" t="inlineStr">
-        <is>
-          <t>Violence against civilians ---- Violence against civilians ---- Violence against civilians ---- Violence against civilians</t>
-        </is>
-      </c>
-      <c r="BE20" t="inlineStr">
-        <is>
-          <t>Attack ---- Abduction/forced disappearance ---- Attack ---- Abduction/forced disappearance</t>
-        </is>
-      </c>
-      <c r="BF20" t="inlineStr">
-        <is>
-          <t>JNIM: Group for Support of Islam and Muslims ---- JNIM: Group for Support of Islam and Muslims ---- Military Forces of Mali (2021-) ---- JNIM: Group for Support of Islam and Muslims</t>
-        </is>
-      </c>
+      <c r="BD20" t="inlineStr"/>
+      <c r="BE20" t="inlineStr"/>
+      <c r="BF20" t="inlineStr"/>
       <c r="BG20" t="inlineStr"/>
-      <c r="BH20" t="inlineStr">
-        <is>
-          <t>Civilians (Mali) ---- Civilians (Mali) ---- Civilians (Mali) ---- Civilians (Mali)</t>
-        </is>
-      </c>
-      <c r="BI20" t="inlineStr">
-        <is>
-          <t>Teachers (Mali) ---- Teachers (Mali) ---- Pastoralists (Mali) ---- Teachers (Mali)</t>
-        </is>
-      </c>
-      <c r="BJ20" t="inlineStr">
-        <is>
-          <t>On 3 January 2024, JNIM militants attacked the village of Tielan (Macina, Segou). The village was burned and two teachers were abducted. Casualties unknown. ---- On 6 January 2024, JNIM militants abducted two teachers in the village of Tielan (Macina, Segou). The abducted were released on 9 January. ---- On 3 June 2024, soldiers securing the basic education diploma (DEF) exams fired heavily at cattle grazing along the irrigation canals of the Niger office and at the pastoralists in Kolongo Tomo (Macina, Segou). A pastoralist was killed, and animals were slaughtered. ---- On 3 January 2025, an armed group (likely JNIM militants, based on location) abducted two teachers in the village of Tielan (Macina, Segou).</t>
-        </is>
-      </c>
-      <c r="BK20" t="inlineStr">
-        <is>
-          <t>2024-01-03 ---- 2024-01-06 ---- 2024-06-03 ---- 2025-01-03</t>
-        </is>
-      </c>
-      <c r="BL20" t="inlineStr">
-        <is>
-          <t>Macina</t>
-        </is>
-      </c>
+      <c r="BH20" t="inlineStr"/>
+      <c r="BI20" t="inlineStr"/>
+      <c r="BJ20" t="inlineStr"/>
+      <c r="BK20" t="inlineStr"/>
+      <c r="BL20" t="inlineStr"/>
       <c r="BM20" t="n">
-        <v>0.04077413716312176</v>
+        <v>0.001673271686481726</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ML0404</t>
+          <t>ML0402</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -3300,49 +3206,49 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ML0702</t>
+          <t>ML0402</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>ML0201;ML0204;ML0206;ML0305;ML0401;ML0403;ML0404;ML0406;ML0407;ML0505;ML0601;ML0605;ML0701;ML0702;ML0703;ML1001</t>
+          <t>ML0402</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>55.5</v>
+        <v>53.2</v>
       </c>
       <c r="I21" t="n">
-        <v>34.5</v>
+        <v>45.7</v>
       </c>
       <c r="J21" t="n">
-        <v>6.4</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>3.6</v>
+        <v>0.1</v>
       </c>
       <c r="L21" t="n">
-        <v>44.5</v>
+        <v>46.8</v>
       </c>
       <c r="M21" t="n">
-        <v>101.18</v>
+        <v>118.58</v>
       </c>
       <c r="N21" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.34</v>
+        <v>0.49</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2</v>
+        <v>0.49</v>
       </c>
       <c r="S21" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
@@ -3354,7 +3260,7 @@
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>6.09</v>
+        <v>7.18</v>
       </c>
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr"/>
@@ -3398,13 +3304,13 @@
       <c r="BK21" t="inlineStr"/>
       <c r="BL21" t="inlineStr"/>
       <c r="BM21" t="n">
-        <v>0.04372566058382414</v>
+        <v>0.01949693019608941</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ML0405</t>
+          <t>ML0403</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -3413,111 +3319,221 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ML0508</t>
+          <t>ML0407</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>ML0107;ML0405;ML0501;ML0503;ML0508;ML0604;ML0803</t>
+          <t>ML0201;ML0204;ML0206;ML0305;ML0401;ML0403;ML0404;ML0406;ML0407;ML0505;ML0601;ML0605;ML0701;ML0702;ML0703;ML1001</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>21</v>
+        <v>38.4</v>
       </c>
       <c r="I22" t="n">
-        <v>76.3</v>
+        <v>56</v>
       </c>
       <c r="J22" t="n">
-        <v>2.6</v>
+        <v>4.9</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="L22" t="n">
-        <v>79</v>
+        <v>61.6</v>
       </c>
       <c r="M22" t="n">
-        <v>238.62</v>
+        <v>123.03</v>
       </c>
       <c r="N22" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>0.55</v>
+        <v>0.41</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.09</v>
+        <v>5.449999999999999</v>
       </c>
       <c r="R22" t="n">
-        <v>10.76</v>
+        <v>2.36</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>0.47</v>
       </c>
       <c r="T22" t="n">
-        <v>15.62</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
-      <c r="AA22" t="inlineStr"/>
-      <c r="AB22" t="inlineStr"/>
-      <c r="AC22" t="inlineStr"/>
-      <c r="AD22" t="inlineStr"/>
-      <c r="AE22" t="inlineStr"/>
-      <c r="AF22" t="inlineStr"/>
-      <c r="AG22" t="inlineStr"/>
-      <c r="AH22" t="inlineStr"/>
-      <c r="AI22" t="inlineStr"/>
-      <c r="AJ22" t="inlineStr"/>
-      <c r="AK22" t="inlineStr"/>
-      <c r="AL22" t="inlineStr"/>
-      <c r="AM22" t="inlineStr"/>
-      <c r="AN22" t="inlineStr"/>
-      <c r="AO22" t="inlineStr"/>
-      <c r="AP22" t="inlineStr"/>
-      <c r="AQ22" t="inlineStr"/>
-      <c r="AR22" t="inlineStr"/>
-      <c r="AS22" t="inlineStr"/>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AU22" t="inlineStr"/>
-      <c r="AV22" t="inlineStr"/>
+        <v>7.96</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>2024-01-06 ---- 2024-01-03</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">January 2024: JNIM militants abducted two educators. They were released 3 days later. ---- January 2024: Two educators kidnapped by JNIM militants and the village burned. Both educators were released on 6 days later. </t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>Unspecified Location ---- Unspecified Location</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>NSA ---- NSA</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>Jama'at Nasr al-Islam wal Muslimin ---- Jama'at Nasr al-Islam wal Muslimin</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr">
+        <is>
+          <t>Firearms ---- Firearms</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>Not Applicable ---- Not Applicable</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>Freed ---- Freed</t>
+        </is>
+      </c>
       <c r="AW22" t="inlineStr"/>
       <c r="AX22" t="inlineStr"/>
-      <c r="AY22" t="inlineStr"/>
-      <c r="AZ22" t="inlineStr"/>
-      <c r="BA22" t="inlineStr"/>
-      <c r="BB22" t="inlineStr"/>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Segou</t>
+        </is>
+      </c>
+      <c r="AZ22" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>ML04</t>
+        </is>
+      </c>
       <c r="BC22" t="inlineStr"/>
-      <c r="BD22" t="inlineStr"/>
-      <c r="BE22" t="inlineStr"/>
-      <c r="BF22" t="inlineStr"/>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>Violence against civilians ---- Violence against civilians ---- Violence against civilians ---- Violence against civilians</t>
+        </is>
+      </c>
+      <c r="BE22" t="inlineStr">
+        <is>
+          <t>Attack ---- Abduction/forced disappearance ---- Attack ---- Abduction/forced disappearance</t>
+        </is>
+      </c>
+      <c r="BF22" t="inlineStr">
+        <is>
+          <t>JNIM: Group for Support of Islam and Muslims ---- JNIM: Group for Support of Islam and Muslims ---- Military Forces of Mali (2021-) ---- JNIM: Group for Support of Islam and Muslims</t>
+        </is>
+      </c>
       <c r="BG22" t="inlineStr"/>
-      <c r="BH22" t="inlineStr"/>
-      <c r="BI22" t="inlineStr"/>
-      <c r="BJ22" t="inlineStr"/>
-      <c r="BK22" t="inlineStr"/>
-      <c r="BL22" t="inlineStr"/>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>Civilians (Mali) ---- Civilians (Mali) ---- Civilians (Mali) ---- Civilians (Mali)</t>
+        </is>
+      </c>
+      <c r="BI22" t="inlineStr">
+        <is>
+          <t>Teachers (Mali) ---- Teachers (Mali) ---- Pastoralists (Mali) ---- Teachers (Mali)</t>
+        </is>
+      </c>
+      <c r="BJ22" t="inlineStr">
+        <is>
+          <t>On 3 January 2024, JNIM militants attacked the village of Tielan (Macina, Segou). The village was burned and two teachers were abducted. Casualties unknown. ---- On 6 January 2024, JNIM militants abducted two teachers in the village of Tielan (Macina, Segou). The abducted were released on 9 January. ---- On 3 June 2024, soldiers securing the basic education diploma (DEF) exams fired heavily at cattle grazing along the irrigation canals of the Niger office and at the pastoralists in Kolongo Tomo (Macina, Segou). A pastoralist was killed, and animals were slaughtered. ---- On 3 January 2025, an armed group (likely JNIM militants, based on location) abducted two teachers in the village of Tielan (Macina, Segou).</t>
+        </is>
+      </c>
+      <c r="BK22" t="inlineStr">
+        <is>
+          <t>2024-01-03 ---- 2024-01-06 ---- 2024-06-03 ---- 2025-01-03</t>
+        </is>
+      </c>
+      <c r="BL22" t="inlineStr">
+        <is>
+          <t>Macina</t>
+        </is>
+      </c>
       <c r="BM22" t="n">
-        <v>0.02998954265356643</v>
+        <v>0.04077413716312176</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ML0406</t>
+          <t>ML0404</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -3526,7 +3542,7 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ML0601</t>
+          <t>ML0702</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3535,52 +3551,52 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>38.7</v>
+        <v>55.5</v>
       </c>
       <c r="I23" t="n">
-        <v>55.1</v>
+        <v>34.5</v>
       </c>
       <c r="J23" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="K23" t="n">
-        <v>0.5</v>
+        <v>3.6</v>
       </c>
       <c r="L23" t="n">
-        <v>61.3</v>
+        <v>44.5</v>
       </c>
       <c r="M23" t="n">
-        <v>90.68000000000001</v>
+        <v>101.18</v>
       </c>
       <c r="N23" t="n">
-        <v>3.32</v>
+        <v>3.08</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.09</v>
+        <v>3.34</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S23" t="n">
-        <v>1.12</v>
+        <v>1.52</v>
       </c>
       <c r="T23" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5600000000000001</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>0.5600000000000001</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0.5600000000000001</v>
+        <v>6.09</v>
       </c>
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr"/>
@@ -3624,13 +3640,13 @@
       <c r="BK23" t="inlineStr"/>
       <c r="BL23" t="inlineStr"/>
       <c r="BM23" t="n">
-        <v>0.1831748603590159</v>
+        <v>0.04372566058382414</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ML0407</t>
+          <t>ML0405</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -3639,61 +3655,61 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ML0403</t>
+          <t>ML0508</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>ML0201;ML0204;ML0206;ML0305;ML0401;ML0403;ML0404;ML0406;ML0407;ML0505;ML0601;ML0605;ML0701;ML0702;ML0703;ML1001</t>
+          <t>ML0107;ML0405;ML0501;ML0503;ML0508;ML0604;ML0803</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="I24" t="n">
-        <v>38.6</v>
+        <v>76.3</v>
       </c>
       <c r="J24" t="n">
-        <v>6.8</v>
+        <v>2.6</v>
       </c>
       <c r="K24" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="M24" t="n">
-        <v>188.76</v>
+        <v>238.62</v>
       </c>
       <c r="N24" t="n">
-        <v>0.6</v>
+        <v>3.29</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="Q24" t="n">
-        <v>10.12</v>
+        <v>1.09</v>
       </c>
       <c r="R24" t="n">
-        <v>0.3</v>
+        <v>10.76</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>15.03</v>
+        <v>15.62</v>
       </c>
       <c r="U24" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="X24" t="inlineStr"/>
       <c r="Y24" t="inlineStr"/>
@@ -3737,13 +3753,13 @@
       <c r="BK24" t="inlineStr"/>
       <c r="BL24" t="inlineStr"/>
       <c r="BM24" t="n">
-        <v>0.02281301631899347</v>
+        <v>0.02998954265356643</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ML0501</t>
+          <t>ML0406</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -3752,217 +3768,111 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ML0508</t>
+          <t>ML0601</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>ML0107;ML0405;ML0501;ML0503;ML0508;ML0604;ML0803</t>
+          <t>ML0201;ML0204;ML0206;ML0305;ML0401;ML0403;ML0404;ML0406;ML0407;ML0505;ML0601;ML0605;ML0701;ML0702;ML0703;ML1001</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>68.5</v>
+        <v>38.7</v>
       </c>
       <c r="I25" t="n">
-        <v>24.3</v>
+        <v>55.1</v>
       </c>
       <c r="J25" t="n">
-        <v>7.2</v>
+        <v>5.7</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L25" t="n">
-        <v>31.5</v>
+        <v>61.3</v>
       </c>
       <c r="M25" t="n">
-        <v>95.03999999999999</v>
+        <v>90.68000000000001</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="O25" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>12.86</v>
+        <v>1.09</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0.93</v>
+        <v>1.12</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>2024-08-25</t>
-        </is>
-      </c>
-      <c r="AP25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">August 2024: A educator was killed by JNIM militants while cultivating his field. </t>
-        </is>
-      </c>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr"/>
+      <c r="AJ25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr"/>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="inlineStr"/>
+      <c r="AO25" t="inlineStr"/>
+      <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr"/>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>NSA</t>
-        </is>
-      </c>
-      <c r="AS25" t="inlineStr">
-        <is>
-          <t>Jama'at Nasr al-Islam wal Muslimin</t>
-        </is>
-      </c>
-      <c r="AT25" t="inlineStr">
-        <is>
-          <t>No Information on the Weapon Used</t>
-        </is>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
+      <c r="AR25" t="inlineStr"/>
+      <c r="AS25" t="inlineStr"/>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AU25" t="inlineStr"/>
       <c r="AV25" t="inlineStr"/>
       <c r="AW25" t="inlineStr"/>
       <c r="AX25" t="inlineStr"/>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>Mopti</t>
-        </is>
-      </c>
-      <c r="AZ25" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB25" t="inlineStr">
-        <is>
-          <t>ML05</t>
-        </is>
-      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr"/>
+      <c r="BA25" t="inlineStr"/>
+      <c r="BB25" t="inlineStr"/>
       <c r="BC25" t="inlineStr"/>
-      <c r="BD25" t="inlineStr">
-        <is>
-          <t>Protests ---- Violence against civilians</t>
-        </is>
-      </c>
-      <c r="BE25" t="inlineStr">
-        <is>
-          <t>Peaceful protest ---- Attack</t>
-        </is>
-      </c>
-      <c r="BF25" t="inlineStr">
-        <is>
-          <t>Protesters (Mali) ---- JNIM: Group for Support of Islam and Muslims</t>
-        </is>
-      </c>
-      <c r="BG25" t="inlineStr">
-        <is>
-          <t>Students (Mali)</t>
-        </is>
-      </c>
-      <c r="BH25" t="inlineStr">
-        <is>
-          <t>Civilians (Mali)</t>
-        </is>
-      </c>
-      <c r="BI25" t="inlineStr">
-        <is>
-          <t>Teachers (Mali)</t>
-        </is>
-      </c>
-      <c r="BJ25" t="inlineStr">
-        <is>
-          <t>On 17 January 2024, a number of students staged a demonstration in the town of Bandiagara (Bandiagara, Mopti) to denounce the lack of teachers at the public high school. The students called on the governor staff to find solutions. ---- On 25 August 2024, likely JNIM militants killed a teacher cultivating his field in Bandiagara (Bandiagara, Mopti).</t>
-        </is>
-      </c>
-      <c r="BK25" t="inlineStr">
-        <is>
-          <t>2024-01-17 ---- 2024-08-25</t>
-        </is>
-      </c>
-      <c r="BL25" t="inlineStr">
-        <is>
-          <t>Bandiagara</t>
-        </is>
-      </c>
+      <c r="BD25" t="inlineStr"/>
+      <c r="BE25" t="inlineStr"/>
+      <c r="BF25" t="inlineStr"/>
+      <c r="BG25" t="inlineStr"/>
+      <c r="BH25" t="inlineStr"/>
+      <c r="BI25" t="inlineStr"/>
+      <c r="BJ25" t="inlineStr"/>
+      <c r="BK25" t="inlineStr"/>
+      <c r="BL25" t="inlineStr"/>
       <c r="BM25" t="n">
-        <v>0.09289959336878323</v>
+        <v>0.1831748603590159</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ML0502</t>
+          <t>ML0407</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -3971,61 +3881,61 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ML0307</t>
+          <t>ML0403</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>ML0307;ML0502;ML0804</t>
+          <t>ML0201;ML0204;ML0206;ML0305;ML0401;ML0403;ML0404;ML0406;ML0407;ML0505;ML0601;ML0605;ML0701;ML0702;ML0703;ML1001</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>40.8</v>
+        <v>54</v>
       </c>
       <c r="I26" t="n">
-        <v>40.2</v>
+        <v>38.6</v>
       </c>
       <c r="J26" t="n">
-        <v>19</v>
+        <v>6.8</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="L26" t="n">
-        <v>59.2</v>
+        <v>46</v>
       </c>
       <c r="M26" t="n">
-        <v>126.25</v>
+        <v>188.76</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>0.8100000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>38.65</v>
+        <v>10.12</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="S26" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>15.03</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="X26" t="inlineStr"/>
       <c r="Y26" t="inlineStr"/>
@@ -4069,13 +3979,13 @@
       <c r="BK26" t="inlineStr"/>
       <c r="BL26" t="inlineStr"/>
       <c r="BM26" t="n">
-        <v>0.0795547108335596</v>
+        <v>0.02281301631899347</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ML0503</t>
+          <t>ML0501</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -4084,7 +3994,7 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ML0405</t>
+          <t>ML0508</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4093,40 +4003,40 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>60.5</v>
+        <v>68.5</v>
       </c>
       <c r="I27" t="n">
-        <v>37.8</v>
+        <v>24.3</v>
       </c>
       <c r="J27" t="n">
-        <v>1.7</v>
+        <v>7.2</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>39.5</v>
+        <v>31.5</v>
       </c>
       <c r="M27" t="n">
-        <v>86.62</v>
+        <v>95.03999999999999</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P27" t="n">
-        <v>0.73</v>
+        <v>1.15</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.76</v>
+        <v>12.86</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="T27" t="n">
         <v>0</v>
@@ -4138,57 +4048,163 @@
         <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
-      <c r="AA27" t="inlineStr"/>
-      <c r="AB27" t="inlineStr"/>
-      <c r="AC27" t="inlineStr"/>
-      <c r="AD27" t="inlineStr"/>
-      <c r="AE27" t="inlineStr"/>
-      <c r="AF27" t="inlineStr"/>
-      <c r="AG27" t="inlineStr"/>
-      <c r="AH27" t="inlineStr"/>
-      <c r="AI27" t="inlineStr"/>
-      <c r="AJ27" t="inlineStr"/>
-      <c r="AK27" t="inlineStr"/>
-      <c r="AL27" t="inlineStr"/>
-      <c r="AM27" t="inlineStr"/>
-      <c r="AN27" t="inlineStr"/>
-      <c r="AO27" t="inlineStr"/>
-      <c r="AP27" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>2024-08-25</t>
+        </is>
+      </c>
+      <c r="AP27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">August 2024: A educator was killed by JNIM militants while cultivating his field. </t>
+        </is>
+      </c>
       <c r="AQ27" t="inlineStr"/>
-      <c r="AR27" t="inlineStr"/>
-      <c r="AS27" t="inlineStr"/>
-      <c r="AT27" t="inlineStr"/>
-      <c r="AU27" t="inlineStr"/>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>NSA</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>Jama'at Nasr al-Islam wal Muslimin</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr">
+        <is>
+          <t>No Information on the Weapon Used</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
       <c r="AV27" t="inlineStr"/>
       <c r="AW27" t="inlineStr"/>
       <c r="AX27" t="inlineStr"/>
-      <c r="AY27" t="inlineStr"/>
-      <c r="AZ27" t="inlineStr"/>
-      <c r="BA27" t="inlineStr"/>
-      <c r="BB27" t="inlineStr"/>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Mopti</t>
+        </is>
+      </c>
+      <c r="AZ27" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB27" t="inlineStr">
+        <is>
+          <t>ML05</t>
+        </is>
+      </c>
       <c r="BC27" t="inlineStr"/>
-      <c r="BD27" t="inlineStr"/>
-      <c r="BE27" t="inlineStr"/>
-      <c r="BF27" t="inlineStr"/>
-      <c r="BG27" t="inlineStr"/>
-      <c r="BH27" t="inlineStr"/>
-      <c r="BI27" t="inlineStr"/>
-      <c r="BJ27" t="inlineStr"/>
-      <c r="BK27" t="inlineStr"/>
-      <c r="BL27" t="inlineStr"/>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>Protests ---- Violence against civilians</t>
+        </is>
+      </c>
+      <c r="BE27" t="inlineStr">
+        <is>
+          <t>Peaceful protest ---- Attack</t>
+        </is>
+      </c>
+      <c r="BF27" t="inlineStr">
+        <is>
+          <t>Protesters (Mali) ---- JNIM: Group for Support of Islam and Muslims</t>
+        </is>
+      </c>
+      <c r="BG27" t="inlineStr">
+        <is>
+          <t>Students (Mali)</t>
+        </is>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>Civilians (Mali)</t>
+        </is>
+      </c>
+      <c r="BI27" t="inlineStr">
+        <is>
+          <t>Teachers (Mali)</t>
+        </is>
+      </c>
+      <c r="BJ27" t="inlineStr">
+        <is>
+          <t>On 17 January 2024, a number of students staged a demonstration in the town of Bandiagara (Bandiagara, Mopti) to denounce the lack of teachers at the public high school. The students called on the governor staff to find solutions. ---- On 25 August 2024, likely JNIM militants killed a teacher cultivating his field in Bandiagara (Bandiagara, Mopti).</t>
+        </is>
+      </c>
+      <c r="BK27" t="inlineStr">
+        <is>
+          <t>2024-01-17 ---- 2024-08-25</t>
+        </is>
+      </c>
+      <c r="BL27" t="inlineStr">
+        <is>
+          <t>Bandiagara</t>
+        </is>
+      </c>
       <c r="BM27" t="n">
-        <v>0.01520097113568924</v>
+        <v>0.09289959336878323</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ML0504</t>
+          <t>ML0502</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -4197,31 +4213,31 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>ML0901</t>
+          <t>ML0307</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>ML0504;ML0901</t>
+          <t>ML0307;ML0502;ML0804</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>74.40000000000001</v>
+        <v>40.8</v>
       </c>
       <c r="I28" t="n">
-        <v>17.2</v>
+        <v>40.2</v>
       </c>
       <c r="J28" t="n">
-        <v>8.300000000000001</v>
+        <v>19</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>25.6</v>
+        <v>59.2</v>
       </c>
       <c r="M28" t="n">
-        <v>97.64999999999999</v>
+        <v>126.25</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -4230,16 +4246,16 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1.71</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Q28" t="n">
-        <v>9.66</v>
+        <v>38.65</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0.23</v>
+        <v>0.8</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -4280,72 +4296,28 @@
       <c r="AV28" t="inlineStr"/>
       <c r="AW28" t="inlineStr"/>
       <c r="AX28" t="inlineStr"/>
-      <c r="AY28" t="inlineStr">
-        <is>
-          <t>Mopti</t>
-        </is>
-      </c>
-      <c r="AZ28" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB28" t="inlineStr">
-        <is>
-          <t>ML05</t>
-        </is>
-      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr"/>
+      <c r="BA28" t="inlineStr"/>
+      <c r="BB28" t="inlineStr"/>
       <c r="BC28" t="inlineStr"/>
-      <c r="BD28" t="inlineStr">
-        <is>
-          <t>Explosions/Remote violence</t>
-        </is>
-      </c>
-      <c r="BE28" t="inlineStr">
-        <is>
-          <t>Air/drone strike</t>
-        </is>
-      </c>
-      <c r="BF28" t="inlineStr">
-        <is>
-          <t>Military Forces of Mali (2021-)</t>
-        </is>
-      </c>
+      <c r="BD28" t="inlineStr"/>
+      <c r="BE28" t="inlineStr"/>
+      <c r="BF28" t="inlineStr"/>
       <c r="BG28" t="inlineStr"/>
-      <c r="BH28" t="inlineStr">
-        <is>
-          <t>Civilians (Mali)</t>
-        </is>
-      </c>
-      <c r="BI28" t="inlineStr">
-        <is>
-          <t>Muslim Group (Mali); Students (Mali)</t>
-        </is>
-      </c>
-      <c r="BJ28" t="inlineStr">
-        <is>
-          <t>On 22 March 2024, the Malian air force carried out airstrikes against a group of Koranic students (children) in the village of Douna (Douentza, Mopti). 14 students were killed and eight were injured.</t>
-        </is>
-      </c>
-      <c r="BK28" t="inlineStr">
-        <is>
-          <t>2024-03-22</t>
-        </is>
-      </c>
-      <c r="BL28" t="inlineStr">
-        <is>
-          <t>Douentza</t>
-        </is>
-      </c>
+      <c r="BH28" t="inlineStr"/>
+      <c r="BI28" t="inlineStr"/>
+      <c r="BJ28" t="inlineStr"/>
+      <c r="BK28" t="inlineStr"/>
+      <c r="BL28" t="inlineStr"/>
       <c r="BM28" t="n">
-        <v>0.001476701619408078</v>
+        <v>0.0795547108335596</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ML0505</t>
+          <t>ML0503</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -4354,61 +4326,61 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ML0407</t>
+          <t>ML0405</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>ML0201;ML0204;ML0206;ML0305;ML0401;ML0403;ML0404;ML0406;ML0407;ML0505;ML0601;ML0605;ML0701;ML0702;ML0703;ML1001</t>
+          <t>ML0107;ML0405;ML0501;ML0503;ML0508;ML0604;ML0803</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>62.5</v>
+        <v>60.5</v>
       </c>
       <c r="I29" t="n">
-        <v>18.1</v>
+        <v>37.8</v>
       </c>
       <c r="J29" t="n">
-        <v>18.1</v>
+        <v>1.7</v>
       </c>
       <c r="K29" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>37.5</v>
+        <v>39.5</v>
       </c>
       <c r="M29" t="n">
-        <v>65.37</v>
+        <v>86.62</v>
       </c>
       <c r="N29" t="n">
-        <v>0.39</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>3.47</v>
+        <v>0.73</v>
       </c>
       <c r="Q29" t="n">
-        <v>24.63</v>
+        <v>2.76</v>
       </c>
       <c r="R29" t="n">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>16.28</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>2.32</v>
+        <v>0.44</v>
       </c>
       <c r="X29" t="inlineStr"/>
       <c r="Y29" t="inlineStr"/>
@@ -4437,68 +4409,28 @@
       <c r="AV29" t="inlineStr"/>
       <c r="AW29" t="inlineStr"/>
       <c r="AX29" t="inlineStr"/>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>Mopti</t>
-        </is>
-      </c>
-      <c r="AZ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB29" t="inlineStr">
-        <is>
-          <t>ML05</t>
-        </is>
-      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr"/>
+      <c r="BA29" t="inlineStr"/>
+      <c r="BB29" t="inlineStr"/>
       <c r="BC29" t="inlineStr"/>
-      <c r="BD29" t="inlineStr">
-        <is>
-          <t>Protests</t>
-        </is>
-      </c>
-      <c r="BE29" t="inlineStr">
-        <is>
-          <t>Peaceful protest</t>
-        </is>
-      </c>
-      <c r="BF29" t="inlineStr">
-        <is>
-          <t>Protesters (Mali)</t>
-        </is>
-      </c>
-      <c r="BG29" t="inlineStr">
-        <is>
-          <t>Teachers (Mali)</t>
-        </is>
-      </c>
+      <c r="BD29" t="inlineStr"/>
+      <c r="BE29" t="inlineStr"/>
+      <c r="BF29" t="inlineStr"/>
+      <c r="BG29" t="inlineStr"/>
       <c r="BH29" t="inlineStr"/>
       <c r="BI29" t="inlineStr"/>
-      <c r="BJ29" t="inlineStr">
-        <is>
-          <t>On 23 February 2024, teachers observed a work stoppage in Koro (Koro, Mopti). The protesters called for the creation of a teaching academy in the circle of Koro.</t>
-        </is>
-      </c>
-      <c r="BK29" t="inlineStr">
-        <is>
-          <t>2024-02-23</t>
-        </is>
-      </c>
-      <c r="BL29" t="inlineStr">
-        <is>
-          <t>Koro</t>
-        </is>
-      </c>
+      <c r="BJ29" t="inlineStr"/>
+      <c r="BK29" t="inlineStr"/>
+      <c r="BL29" t="inlineStr"/>
       <c r="BM29" t="n">
-        <v>0.02566964285714286</v>
+        <v>0.01520097113568924</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ML0506</t>
+          <t>ML0504</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -4507,31 +4439,31 @@
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ML0602</t>
+          <t>ML0901</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>ML0202;ML0205;ML0506;ML0507;ML0602;ML0603</t>
+          <t>ML0504;ML0901</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>67.40000000000001</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>30.5</v>
+        <v>17.2</v>
       </c>
       <c r="J30" t="n">
-        <v>2.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>32.6</v>
+        <v>25.6</v>
       </c>
       <c r="M30" t="n">
-        <v>125.99</v>
+        <v>97.64999999999999</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -4540,16 +4472,16 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>3.71</v>
+        <v>1.71</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.58</v>
+        <v>9.66</v>
       </c>
       <c r="R30" t="n">
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0.62</v>
+        <v>0.23</v>
       </c>
       <c r="T30" t="n">
         <v>0</v>
@@ -4596,10 +4528,10 @@
         </is>
       </c>
       <c r="AZ30" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="BA30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
@@ -4609,57 +4541,53 @@
       <c r="BC30" t="inlineStr"/>
       <c r="BD30" t="inlineStr">
         <is>
-          <t>Strategic developments ---- Violence against civilians ---- Violence against civilians ---- Violence against civilians</t>
+          <t>Explosions/Remote violence</t>
         </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
-          <t>Arrests ---- Attack ---- Abduction/forced disappearance ---- Attack</t>
+          <t>Air/drone strike</t>
         </is>
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>Military Forces of Mali (2021-) ---- JNIM: Group for Support of Islam and Muslims ---- JNIM: Group for Support of Islam and Muslims ---- JNIM: Group for Support of Islam and Muslims</t>
-        </is>
-      </c>
-      <c r="BG30" t="inlineStr">
-        <is>
-          <t>Wagner Group</t>
-        </is>
-      </c>
+          <t>Military Forces of Mali (2021-)</t>
+        </is>
+      </c>
+      <c r="BG30" t="inlineStr"/>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>Civilians (Mali) ---- Civilians (Mali) ---- Civilians (Mali) ---- Civilians (Mali)</t>
+          <t>Civilians (Mali)</t>
         </is>
       </c>
       <c r="BI30" t="inlineStr">
         <is>
-          <t>Fulani Ethnic Group (Mali); Pastoralists (Mali); Students (Mali) ---- Muslim Group (Mali) ---- Muslim Group (Mali) ---- Muslim Group (Mali)</t>
+          <t>Muslim Group (Mali); Students (Mali)</t>
         </is>
       </c>
       <c r="BJ30" t="inlineStr">
         <is>
-          <t>On 5 March 2024, FAMA and Wagner forces arrested several students from Fulani community in the town of Sevare (Mopti, Mopti). ---- Around 15 August 2024 (month of), JNIM militants killed at least one adolescent Quranic school student (Talibe) in the village of Niakongo (Mopti, Mopti). ---- On 31 October 2024, JNIM militants abducted a coranic school teacher in Sevare (Mopti, Mopti) ---- On 9 November 2024, JNIM militants killed two adolescent Quranic school students (Talibes) in the village of Niakongo (Mopti, Mopti).</t>
+          <t>On 22 March 2024, the Malian air force carried out airstrikes against a group of Koranic students (children) in the village of Douna (Douentza, Mopti). 14 students were killed and eight were injured.</t>
         </is>
       </c>
       <c r="BK30" t="inlineStr">
         <is>
-          <t>2024-03-05 ---- 2024-08-15 ---- 2024-10-31 ---- 2024-11-09</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="BL30" t="inlineStr">
         <is>
-          <t>Mopti</t>
+          <t>Douentza</t>
         </is>
       </c>
       <c r="BM30" t="n">
-        <v>0.1495662714496761</v>
+        <v>0.001476701619408078</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ML0507</t>
+          <t>ML0505</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -4668,61 +4596,61 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>ML0205</t>
+          <t>ML0407</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>ML0202;ML0205;ML0506;ML0507;ML0602;ML0603</t>
+          <t>ML0201;ML0204;ML0206;ML0305;ML0401;ML0403;ML0404;ML0406;ML0407;ML0505;ML0601;ML0605;ML0701;ML0702;ML0703;ML1001</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>36.2</v>
+        <v>62.5</v>
       </c>
       <c r="I31" t="n">
-        <v>57.9</v>
+        <v>18.1</v>
       </c>
       <c r="J31" t="n">
-        <v>5.9</v>
+        <v>18.1</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="L31" t="n">
-        <v>63.8</v>
+        <v>37.5</v>
       </c>
       <c r="M31" t="n">
-        <v>108.7</v>
+        <v>65.37</v>
       </c>
       <c r="N31" t="n">
-        <v>0.76</v>
+        <v>0.39</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>6.380000000000001</v>
+        <v>3.47</v>
       </c>
       <c r="Q31" t="n">
-        <v>12.92</v>
+        <v>24.63</v>
       </c>
       <c r="R31" t="n">
-        <v>0.38</v>
+        <v>0.28</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="T31" t="n">
-        <v>7.57</v>
+        <v>16.28</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="X31" t="inlineStr"/>
       <c r="Y31" t="inlineStr"/>
@@ -4751,28 +4679,68 @@
       <c r="AV31" t="inlineStr"/>
       <c r="AW31" t="inlineStr"/>
       <c r="AX31" t="inlineStr"/>
-      <c r="AY31" t="inlineStr"/>
-      <c r="AZ31" t="inlineStr"/>
-      <c r="BA31" t="inlineStr"/>
-      <c r="BB31" t="inlineStr"/>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Mopti</t>
+        </is>
+      </c>
+      <c r="AZ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB31" t="inlineStr">
+        <is>
+          <t>ML05</t>
+        </is>
+      </c>
       <c r="BC31" t="inlineStr"/>
-      <c r="BD31" t="inlineStr"/>
-      <c r="BE31" t="inlineStr"/>
-      <c r="BF31" t="inlineStr"/>
-      <c r="BG31" t="inlineStr"/>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>Protests</t>
+        </is>
+      </c>
+      <c r="BE31" t="inlineStr">
+        <is>
+          <t>Peaceful protest</t>
+        </is>
+      </c>
+      <c r="BF31" t="inlineStr">
+        <is>
+          <t>Protesters (Mali)</t>
+        </is>
+      </c>
+      <c r="BG31" t="inlineStr">
+        <is>
+          <t>Teachers (Mali)</t>
+        </is>
+      </c>
       <c r="BH31" t="inlineStr"/>
       <c r="BI31" t="inlineStr"/>
-      <c r="BJ31" t="inlineStr"/>
-      <c r="BK31" t="inlineStr"/>
-      <c r="BL31" t="inlineStr"/>
+      <c r="BJ31" t="inlineStr">
+        <is>
+          <t>On 23 February 2024, teachers observed a work stoppage in Koro (Koro, Mopti). The protesters called for the creation of a teaching academy in the circle of Koro.</t>
+        </is>
+      </c>
+      <c r="BK31" t="inlineStr">
+        <is>
+          <t>2024-02-23</t>
+        </is>
+      </c>
+      <c r="BL31" t="inlineStr">
+        <is>
+          <t>Koro</t>
+        </is>
+      </c>
       <c r="BM31" t="n">
-        <v>0.03256678600936381</v>
+        <v>0.02566964285714286</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ML0508</t>
+          <t>ML0506</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -4781,31 +4749,31 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ML0604</t>
+          <t>ML0602</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>ML0107;ML0405;ML0501;ML0503;ML0508;ML0604;ML0803</t>
+          <t>ML0202;ML0205;ML0506;ML0507;ML0602;ML0603</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>25.6</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>65.59999999999999</v>
+        <v>30.5</v>
       </c>
       <c r="J32" t="n">
-        <v>8.699999999999999</v>
+        <v>2.1</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>74.40000000000001</v>
+        <v>32.6</v>
       </c>
       <c r="M32" t="n">
-        <v>126.58</v>
+        <v>125.99</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -4814,16 +4782,16 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>8.44</v>
+        <v>3.71</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="R32" t="n">
         <v>0.84</v>
       </c>
       <c r="S32" t="n">
-        <v>19.09</v>
+        <v>0.62</v>
       </c>
       <c r="T32" t="n">
         <v>0</v>
@@ -4835,7 +4803,7 @@
         <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="X32" t="inlineStr"/>
       <c r="Y32" t="inlineStr"/>
@@ -4870,10 +4838,10 @@
         </is>
       </c>
       <c r="AZ32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BA32" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
@@ -4883,49 +4851,57 @@
       <c r="BC32" t="inlineStr"/>
       <c r="BD32" t="inlineStr">
         <is>
-          <t>Protests ---- Protests</t>
+          <t>Strategic developments ---- Violence against civilians ---- Violence against civilians ---- Violence against civilians</t>
         </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
-          <t>Peaceful protest ---- Peaceful protest</t>
+          <t>Arrests ---- Attack ---- Abduction/forced disappearance ---- Attack</t>
         </is>
       </c>
       <c r="BF32" t="inlineStr">
         <is>
-          <t>Protesters (Mali) ---- Protesters (Mali)</t>
+          <t>Military Forces of Mali (2021-) ---- JNIM: Group for Support of Islam and Muslims ---- JNIM: Group for Support of Islam and Muslims ---- JNIM: Group for Support of Islam and Muslims</t>
         </is>
       </c>
       <c r="BG32" t="inlineStr">
         <is>
-          <t>Students (Mali) ---- Students (Mali)</t>
-        </is>
-      </c>
-      <c r="BH32" t="inlineStr"/>
-      <c r="BI32" t="inlineStr"/>
+          <t>Wagner Group</t>
+        </is>
+      </c>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>Civilians (Mali) ---- Civilians (Mali) ---- Civilians (Mali) ---- Civilians (Mali)</t>
+        </is>
+      </c>
+      <c r="BI32" t="inlineStr">
+        <is>
+          <t>Fulani Ethnic Group (Mali); Pastoralists (Mali); Students (Mali) ---- Muslim Group (Mali) ---- Muslim Group (Mali) ---- Muslim Group (Mali)</t>
+        </is>
+      </c>
       <c r="BJ32" t="inlineStr">
         <is>
-          <t>Around 9 January 2025 (between 6 - 12 January), students from the public high school staged a peaceful demonstration in the town of Youwarou (Youwarou, Mopti). They protested against the lack of teachers in the school. ---- On 14 January 2025, students from the public high school staged a peaceful demonstration in the town of Youwarou (Youwarou, Mopti). They protested against the transfer of a literature teacher to another town, at a time when the school is facing a teacher shortage.</t>
+          <t>On 5 March 2024, FAMA and Wagner forces arrested several students from Fulani community in the town of Sevare (Mopti, Mopti). ---- Around 15 August 2024 (month of), JNIM militants killed at least one adolescent Quranic school student (Talibe) in the village of Niakongo (Mopti, Mopti). ---- On 31 October 2024, JNIM militants abducted a coranic school teacher in Sevare (Mopti, Mopti) ---- On 9 November 2024, JNIM militants killed two adolescent Quranic school students (Talibes) in the village of Niakongo (Mopti, Mopti).</t>
         </is>
       </c>
       <c r="BK32" t="inlineStr">
         <is>
-          <t>2025-01-09 ---- 2025-01-14</t>
+          <t>2024-03-05 ---- 2024-08-15 ---- 2024-10-31 ---- 2024-11-09</t>
         </is>
       </c>
       <c r="BL32" t="inlineStr">
         <is>
-          <t>Youwarou</t>
+          <t>Mopti</t>
         </is>
       </c>
       <c r="BM32" t="n">
-        <v>0.04480656990857911</v>
+        <v>0.1495662714496761</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ML0601</t>
+          <t>ML0507</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -4934,52 +4910,52 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ML0406</t>
+          <t>ML0205</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>ML0201;ML0204;ML0206;ML0305;ML0401;ML0403;ML0404;ML0406;ML0407;ML0505;ML0601;ML0605;ML0701;ML0702;ML0703;ML1001</t>
+          <t>ML0202;ML0205;ML0506;ML0507;ML0602;ML0603</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>14.7</v>
+        <v>36.2</v>
       </c>
       <c r="I33" t="n">
-        <v>79.7</v>
+        <v>57.9</v>
       </c>
       <c r="J33" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="K33" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>85.3</v>
+        <v>63.8</v>
       </c>
       <c r="M33" t="n">
-        <v>76.14</v>
+        <v>108.7</v>
       </c>
       <c r="N33" t="n">
-        <v>0.51</v>
+        <v>0.76</v>
       </c>
       <c r="O33" t="n">
-        <v>0.51</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>6.380000000000001</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.52</v>
+        <v>12.92</v>
       </c>
       <c r="R33" t="n">
-        <v>1.52</v>
+        <v>0.38</v>
       </c>
       <c r="S33" t="n">
-        <v>0.51</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>0.51</v>
+        <v>7.57</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
@@ -4988,7 +4964,7 @@
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>0.51</v>
+        <v>0</v>
       </c>
       <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr"/>
@@ -5017,68 +4993,28 @@
       <c r="AV33" t="inlineStr"/>
       <c r="AW33" t="inlineStr"/>
       <c r="AX33" t="inlineStr"/>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>Tombouctou</t>
-        </is>
-      </c>
-      <c r="AZ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB33" t="inlineStr">
-        <is>
-          <t>ML06</t>
-        </is>
-      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr"/>
+      <c r="BA33" t="inlineStr"/>
+      <c r="BB33" t="inlineStr"/>
       <c r="BC33" t="inlineStr"/>
-      <c r="BD33" t="inlineStr">
-        <is>
-          <t>Protests</t>
-        </is>
-      </c>
-      <c r="BE33" t="inlineStr">
-        <is>
-          <t>Peaceful protest</t>
-        </is>
-      </c>
-      <c r="BF33" t="inlineStr">
-        <is>
-          <t>Protesters (Mali)</t>
-        </is>
-      </c>
-      <c r="BG33" t="inlineStr">
-        <is>
-          <t>Labor Group (Mali); Teachers (Mali)</t>
-        </is>
-      </c>
+      <c r="BD33" t="inlineStr"/>
+      <c r="BE33" t="inlineStr"/>
+      <c r="BF33" t="inlineStr"/>
+      <c r="BG33" t="inlineStr"/>
       <c r="BH33" t="inlineStr"/>
       <c r="BI33" t="inlineStr"/>
-      <c r="BJ33" t="inlineStr">
-        <is>
-          <t>On 22 April 2024, teachers observed a work stoppage in the circle of Dire (Dire, Tombouctou). They protested against the decision of the director of the Timbuktu education academy who, in a letter, invited them to travel to Timbuktu for physical presence confirmation.</t>
-        </is>
-      </c>
-      <c r="BK33" t="inlineStr">
-        <is>
-          <t>2024-04-22</t>
-        </is>
-      </c>
-      <c r="BL33" t="inlineStr">
-        <is>
-          <t>Dire</t>
-        </is>
-      </c>
+      <c r="BJ33" t="inlineStr"/>
+      <c r="BK33" t="inlineStr"/>
+      <c r="BL33" t="inlineStr"/>
       <c r="BM33" t="n">
-        <v>0</v>
+        <v>0.03256678600936381</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ML0602</t>
+          <t>ML0508</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -5087,52 +5023,52 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ML0603</t>
+          <t>ML0604</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>ML0202;ML0205;ML0506;ML0507;ML0602;ML0603</t>
+          <t>ML0107;ML0405;ML0501;ML0503;ML0508;ML0604;ML0803</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>37.3</v>
+        <v>25.6</v>
       </c>
       <c r="I34" t="n">
-        <v>49.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="J34" t="n">
-        <v>13.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>62.7</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="M34" t="n">
-        <v>100.09</v>
+        <v>126.58</v>
       </c>
       <c r="N34" t="n">
-        <v>16.42</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.09</v>
+        <v>8.44</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="S34" t="n">
-        <v>1.2</v>
+        <v>19.09</v>
       </c>
       <c r="T34" t="n">
-        <v>0.39</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
@@ -5141,167 +5077,97 @@
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>2024-02-04</t>
-        </is>
-      </c>
-      <c r="AP34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">February 2024: a school director, his son and another civilian were killed by FaMa and Wagner forces. </t>
-        </is>
-      </c>
-      <c r="AQ34" t="inlineStr">
-        <is>
-          <t>Unspecified Location</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>Multiple</t>
-        </is>
-      </c>
-      <c r="AS34" t="inlineStr">
-        <is>
-          <t>Mali Armed Forces, Wagner Group</t>
-        </is>
-      </c>
-      <c r="AT34" t="inlineStr">
-        <is>
-          <t>Firearms</t>
-        </is>
-      </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
+        <v>0.84</v>
+      </c>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr"/>
+      <c r="AE34" t="inlineStr"/>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr"/>
+      <c r="AI34" t="inlineStr"/>
+      <c r="AJ34" t="inlineStr"/>
+      <c r="AK34" t="inlineStr"/>
+      <c r="AL34" t="inlineStr"/>
+      <c r="AM34" t="inlineStr"/>
+      <c r="AN34" t="inlineStr"/>
+      <c r="AO34" t="inlineStr"/>
+      <c r="AP34" t="inlineStr"/>
+      <c r="AQ34" t="inlineStr"/>
+      <c r="AR34" t="inlineStr"/>
+      <c r="AS34" t="inlineStr"/>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AU34" t="inlineStr"/>
       <c r="AV34" t="inlineStr"/>
       <c r="AW34" t="inlineStr"/>
       <c r="AX34" t="inlineStr"/>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>Tombouctou</t>
+          <t>Mopti</t>
         </is>
       </c>
       <c r="AZ34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA34" t="n">
         <v>2</v>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>ML06</t>
+          <t>ML05</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr"/>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>Violence against civilians ---- Violence against civilians</t>
+          <t>Protests ---- Protests</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
-          <t>Attack ---- Abduction/forced disappearance</t>
+          <t>Peaceful protest ---- Peaceful protest</t>
         </is>
       </c>
       <c r="BF34" t="inlineStr">
         <is>
-          <t>Military Forces of Mali (2021-) ---- JNIM: Group for Support of Islam and Muslims</t>
+          <t>Protesters (Mali) ---- Protesters (Mali)</t>
         </is>
       </c>
       <c r="BG34" t="inlineStr">
         <is>
-          <t>Wagner Group</t>
-        </is>
-      </c>
-      <c r="BH34" t="inlineStr">
-        <is>
-          <t>Civilians (Mali) ---- Civilians (Mali)</t>
-        </is>
-      </c>
-      <c r="BI34" t="inlineStr">
-        <is>
-          <t>Teachers (Mali) ---- Muslim Group (Mali); Teachers (Mali)</t>
-        </is>
-      </c>
+          <t>Students (Mali) ---- Students (Mali)</t>
+        </is>
+      </c>
+      <c r="BH34" t="inlineStr"/>
+      <c r="BI34" t="inlineStr"/>
       <c r="BJ34" t="inlineStr">
         <is>
-          <t>On 4 February 2024, FAMa and Wagner forces killed two civilians including a school director and his son in the town of Essakane (Goundam, Tombouctou). ---- On 21 July 2025, suspected JNIM militants abducted a coranic school teacher in the town of Douekire (Goundam, Tombouctou)</t>
+          <t>Around 9 January 2025 (between 6 - 12 January), students from the public high school staged a peaceful demonstration in the town of Youwarou (Youwarou, Mopti). They protested against the lack of teachers in the school. ---- On 14 January 2025, students from the public high school staged a peaceful demonstration in the town of Youwarou (Youwarou, Mopti). They protested against the transfer of a literature teacher to another town, at a time when the school is facing a teacher shortage.</t>
         </is>
       </c>
       <c r="BK34" t="inlineStr">
         <is>
-          <t>2024-02-04 ---- 2025-07-21</t>
+          <t>2025-01-09 ---- 2025-01-14</t>
         </is>
       </c>
       <c r="BL34" t="inlineStr">
         <is>
-          <t>Goundam</t>
+          <t>Youwarou</t>
         </is>
       </c>
       <c r="BM34" t="n">
-        <v>0.02587424719323899</v>
+        <v>0.04480656990857911</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ML0603</t>
+          <t>ML0601</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -5310,52 +5176,52 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ML0202</t>
+          <t>ML0406</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>ML0202;ML0205;ML0506;ML0507;ML0602;ML0603</t>
+          <t>ML0201;ML0204;ML0206;ML0305;ML0401;ML0403;ML0404;ML0406;ML0407;ML0505;ML0601;ML0605;ML0701;ML0702;ML0703;ML1001</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>32.5</v>
+        <v>14.7</v>
       </c>
       <c r="I35" t="n">
-        <v>62</v>
+        <v>79.7</v>
       </c>
       <c r="J35" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L35" t="n">
-        <v>67.5</v>
+        <v>85.3</v>
       </c>
       <c r="M35" t="n">
-        <v>183.43</v>
+        <v>76.14</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="R35" t="n">
-        <v>33.76</v>
+        <v>1.52</v>
       </c>
       <c r="S35" t="n">
-        <v>0.43</v>
+        <v>0.51</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
@@ -5364,7 +5230,7 @@
         <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="X35" t="inlineStr"/>
       <c r="Y35" t="inlineStr"/>
@@ -5402,7 +5268,7 @@
         <v>0</v>
       </c>
       <c r="BA35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
@@ -5412,49 +5278,49 @@
       <c r="BC35" t="inlineStr"/>
       <c r="BD35" t="inlineStr">
         <is>
-          <t>Protests ---- Protests</t>
+          <t>Protests</t>
         </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
-          <t>Peaceful protest ---- Peaceful protest</t>
+          <t>Peaceful protest</t>
         </is>
       </c>
       <c r="BF35" t="inlineStr">
         <is>
-          <t>Protesters (Mali) ---- Protesters (Mali)</t>
+          <t>Protesters (Mali)</t>
         </is>
       </c>
       <c r="BG35" t="inlineStr">
         <is>
-          <t>Labor Group (Mali); Teachers (Mali) ---- Labor Group (Mali); Teachers (Mali)</t>
+          <t>Labor Group (Mali); Teachers (Mali)</t>
         </is>
       </c>
       <c r="BH35" t="inlineStr"/>
       <c r="BI35" t="inlineStr"/>
       <c r="BJ35" t="inlineStr">
         <is>
-          <t>On 24 April 2024, teachers renewed the work 72hours-stoppage in Gourma-Rharous (Gourma-Rharous, Tombouctou). The protesters called for an enrolment team to arrive at the Gourma-Rharous Academy to enroll teachers. ---- On 29 April 2024, teachers renewed the work 72hours-stoppage in Gourma-Rharous (Gourma-Rharous, Tombouctou). They protested called for an enrolment team to arrive at the Gourma-Rharous Academy to enroll teachers.</t>
+          <t>On 22 April 2024, teachers observed a work stoppage in the circle of Dire (Dire, Tombouctou). They protested against the decision of the director of the Timbuktu education academy who, in a letter, invited them to travel to Timbuktu for physical presence confirmation.</t>
         </is>
       </c>
       <c r="BK35" t="inlineStr">
         <is>
-          <t>2024-04-24 ---- 2024-04-29</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="BL35" t="inlineStr">
         <is>
-          <t>Gourma-Rharous</t>
+          <t>Dire</t>
         </is>
       </c>
       <c r="BM35" t="n">
-        <v>0.05394237753207973</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ML0604</t>
+          <t>ML0602</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -5463,55 +5329,55 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ML0508</t>
+          <t>ML0603</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>ML0107;ML0405;ML0501;ML0503;ML0508;ML0604;ML0803</t>
+          <t>ML0202;ML0205;ML0506;ML0507;ML0602;ML0603</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>10.3</v>
+        <v>37.3</v>
       </c>
       <c r="I36" t="n">
-        <v>74.5</v>
+        <v>49.5</v>
       </c>
       <c r="J36" t="n">
-        <v>15.2</v>
+        <v>13.3</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>89.7</v>
+        <v>62.7</v>
       </c>
       <c r="M36" t="n">
-        <v>72.28</v>
+        <v>100.09</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>16.42</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>0.39</v>
       </c>
       <c r="U36" t="n">
-        <v>15.22</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -5538,13 +5404,13 @@
         <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE36" t="n">
         <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -5572,12 +5438,12 @@
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t xml:space="preserve">August 2024: Two school principals were kidnapped by JNIM militants. Their bodies were found 3 days later outside the village health centre. </t>
+          <t xml:space="preserve">February 2024: a school director, his son and another civilian were killed by FaMa and Wagner forces. </t>
         </is>
       </c>
       <c r="AQ36" t="inlineStr">
@@ -5587,17 +5453,17 @@
       </c>
       <c r="AR36" t="inlineStr">
         <is>
-          <t>NSA</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr">
         <is>
-          <t>Jama'at Nasr al-Islam wal Muslimin</t>
+          <t>Mali Armed Forces, Wagner Group</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr">
         <is>
-          <t>No Information on the Weapon Used</t>
+          <t>Firearms</t>
         </is>
       </c>
       <c r="AU36" t="inlineStr">
@@ -5605,11 +5471,7 @@
           <t>Not Applicable</t>
         </is>
       </c>
-      <c r="AV36" t="inlineStr">
-        <is>
-          <t>Killed</t>
-        </is>
-      </c>
+      <c r="AV36" t="inlineStr"/>
       <c r="AW36" t="inlineStr"/>
       <c r="AX36" t="inlineStr"/>
       <c r="AY36" t="inlineStr">
@@ -5636,15 +5498,19 @@
       </c>
       <c r="BE36" t="inlineStr">
         <is>
-          <t>Abduction/forced disappearance ---- Attack</t>
+          <t>Attack ---- Abduction/forced disappearance</t>
         </is>
       </c>
       <c r="BF36" t="inlineStr">
         <is>
-          <t>JNIM: Group for Support of Islam and Muslims ---- JNIM: Group for Support of Islam and Muslims</t>
-        </is>
-      </c>
-      <c r="BG36" t="inlineStr"/>
+          <t>Military Forces of Mali (2021-) ---- JNIM: Group for Support of Islam and Muslims</t>
+        </is>
+      </c>
+      <c r="BG36" t="inlineStr">
+        <is>
+          <t>Wagner Group</t>
+        </is>
+      </c>
       <c r="BH36" t="inlineStr">
         <is>
           <t>Civilians (Mali) ---- Civilians (Mali)</t>
@@ -5652,32 +5518,32 @@
       </c>
       <c r="BI36" t="inlineStr">
         <is>
-          <t>Teachers (Mali) ---- Teachers (Mali)</t>
+          <t>Teachers (Mali) ---- Muslim Group (Mali); Teachers (Mali)</t>
         </is>
       </c>
       <c r="BJ36" t="inlineStr">
         <is>
-          <t>On 15 August 2024, JNIM abducted two school principals near the village of Arabebe (Niafunke, Tombouctou). ---- On 18 August 2024, JNIM militants killed two school principals in the village of Arabebe (Niafunke, Tombouctou). The lifeless bodies of the school principals were found near the village health center.</t>
+          <t>On 4 February 2024, FAMa and Wagner forces killed two civilians including a school director and his son in the town of Essakane (Goundam, Tombouctou). ---- On 21 July 2025, suspected JNIM militants abducted a coranic school teacher in the town of Douekire (Goundam, Tombouctou)</t>
         </is>
       </c>
       <c r="BK36" t="inlineStr">
         <is>
-          <t>2024-08-15 ---- 2024-08-18</t>
+          <t>2024-02-04 ---- 2025-07-21</t>
         </is>
       </c>
       <c r="BL36" t="inlineStr">
         <is>
-          <t>Niafunke</t>
+          <t>Goundam</t>
         </is>
       </c>
       <c r="BM36" t="n">
-        <v>0</v>
+        <v>0.02587424719323899</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ML0605</t>
+          <t>ML0603</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -5686,61 +5552,61 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ML1001</t>
+          <t>ML0202</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>ML0201;ML0204;ML0206;ML0305;ML0401;ML0403;ML0404;ML0406;ML0407;ML0505;ML0601;ML0605;ML0701;ML0702;ML0703;ML1001</t>
+          <t>ML0202;ML0205;ML0506;ML0507;ML0602;ML0603</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>36.8</v>
+        <v>32.5</v>
       </c>
       <c r="I37" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J37" t="n">
-        <v>2.1</v>
+        <v>5.5</v>
       </c>
       <c r="K37" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>63.2</v>
+        <v>67.5</v>
       </c>
       <c r="M37" t="n">
-        <v>143.88</v>
+        <v>183.43</v>
       </c>
       <c r="N37" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>33.76</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>0.43</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="X37" t="inlineStr"/>
       <c r="Y37" t="inlineStr"/>
@@ -5769,28 +5635,68 @@
       <c r="AV37" t="inlineStr"/>
       <c r="AW37" t="inlineStr"/>
       <c r="AX37" t="inlineStr"/>
-      <c r="AY37" t="inlineStr"/>
-      <c r="AZ37" t="inlineStr"/>
-      <c r="BA37" t="inlineStr"/>
-      <c r="BB37" t="inlineStr"/>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Tombouctou</t>
+        </is>
+      </c>
+      <c r="AZ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB37" t="inlineStr">
+        <is>
+          <t>ML06</t>
+        </is>
+      </c>
       <c r="BC37" t="inlineStr"/>
-      <c r="BD37" t="inlineStr"/>
-      <c r="BE37" t="inlineStr"/>
-      <c r="BF37" t="inlineStr"/>
-      <c r="BG37" t="inlineStr"/>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>Protests ---- Protests</t>
+        </is>
+      </c>
+      <c r="BE37" t="inlineStr">
+        <is>
+          <t>Peaceful protest ---- Peaceful protest</t>
+        </is>
+      </c>
+      <c r="BF37" t="inlineStr">
+        <is>
+          <t>Protesters (Mali) ---- Protesters (Mali)</t>
+        </is>
+      </c>
+      <c r="BG37" t="inlineStr">
+        <is>
+          <t>Labor Group (Mali); Teachers (Mali) ---- Labor Group (Mali); Teachers (Mali)</t>
+        </is>
+      </c>
       <c r="BH37" t="inlineStr"/>
       <c r="BI37" t="inlineStr"/>
-      <c r="BJ37" t="inlineStr"/>
-      <c r="BK37" t="inlineStr"/>
-      <c r="BL37" t="inlineStr"/>
+      <c r="BJ37" t="inlineStr">
+        <is>
+          <t>On 24 April 2024, teachers renewed the work 72hours-stoppage in Gourma-Rharous (Gourma-Rharous, Tombouctou). The protesters called for an enrolment team to arrive at the Gourma-Rharous Academy to enroll teachers. ---- On 29 April 2024, teachers renewed the work 72hours-stoppage in Gourma-Rharous (Gourma-Rharous, Tombouctou). They protested called for an enrolment team to arrive at the Gourma-Rharous Academy to enroll teachers.</t>
+        </is>
+      </c>
+      <c r="BK37" t="inlineStr">
+        <is>
+          <t>2024-04-24 ---- 2024-04-29</t>
+        </is>
+      </c>
+      <c r="BL37" t="inlineStr">
+        <is>
+          <t>Gourma-Rharous</t>
+        </is>
+      </c>
       <c r="BM37" t="n">
-        <v>0.09848373541770739</v>
+        <v>0.05394237753207973</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ML0701</t>
+          <t>ML0604</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -5799,31 +5705,31 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>ML0703</t>
+          <t>ML0508</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>ML0201;ML0204;ML0206;ML0305;ML0401;ML0403;ML0404;ML0406;ML0407;ML0505;ML0601;ML0605;ML0701;ML0702;ML0703;ML1001</t>
+          <t>ML0107;ML0405;ML0501;ML0503;ML0508;ML0604;ML0803</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>58.8</v>
+        <v>10.3</v>
       </c>
       <c r="I38" t="n">
-        <v>39.9</v>
+        <v>74.5</v>
       </c>
       <c r="J38" t="n">
-        <v>0.8</v>
+        <v>15.2</v>
       </c>
       <c r="K38" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>41.2</v>
+        <v>89.7</v>
       </c>
       <c r="M38" t="n">
-        <v>142.17</v>
+        <v>72.28</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -5835,10 +5741,10 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>5.42</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>0.61</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -5847,107 +5753,173 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>15.22</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="X38" t="inlineStr"/>
-      <c r="Y38" t="inlineStr"/>
-      <c r="Z38" t="inlineStr"/>
-      <c r="AA38" t="inlineStr"/>
-      <c r="AB38" t="inlineStr"/>
-      <c r="AC38" t="inlineStr"/>
-      <c r="AD38" t="inlineStr"/>
-      <c r="AE38" t="inlineStr"/>
-      <c r="AF38" t="inlineStr"/>
-      <c r="AG38" t="inlineStr"/>
-      <c r="AH38" t="inlineStr"/>
-      <c r="AI38" t="inlineStr"/>
-      <c r="AJ38" t="inlineStr"/>
-      <c r="AK38" t="inlineStr"/>
-      <c r="AL38" t="inlineStr"/>
-      <c r="AM38" t="inlineStr"/>
-      <c r="AN38" t="inlineStr"/>
-      <c r="AO38" t="inlineStr"/>
-      <c r="AP38" t="inlineStr"/>
-      <c r="AQ38" t="inlineStr"/>
-      <c r="AR38" t="inlineStr"/>
-      <c r="AS38" t="inlineStr"/>
-      <c r="AT38" t="inlineStr"/>
-      <c r="AU38" t="inlineStr"/>
-      <c r="AV38" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AP38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">August 2024: Two school principals were kidnapped by JNIM militants. Their bodies were found 3 days later outside the village health centre. </t>
+        </is>
+      </c>
+      <c r="AQ38" t="inlineStr">
+        <is>
+          <t>Unspecified Location</t>
+        </is>
+      </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>NSA</t>
+        </is>
+      </c>
+      <c r="AS38" t="inlineStr">
+        <is>
+          <t>Jama'at Nasr al-Islam wal Muslimin</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr">
+        <is>
+          <t>No Information on the Weapon Used</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="AV38" t="inlineStr">
+        <is>
+          <t>Killed</t>
+        </is>
+      </c>
       <c r="AW38" t="inlineStr"/>
       <c r="AX38" t="inlineStr"/>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>Gao</t>
+          <t>Tombouctou</t>
         </is>
       </c>
       <c r="AZ38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB38" t="inlineStr">
         <is>
-          <t>ML07</t>
+          <t>ML06</t>
         </is>
       </c>
       <c r="BC38" t="inlineStr"/>
       <c r="BD38" t="inlineStr">
         <is>
-          <t>Violence against civilians</t>
+          <t>Violence against civilians ---- Violence against civilians</t>
         </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>Abduction/forced disappearance ---- Attack</t>
         </is>
       </c>
       <c r="BF38" t="inlineStr">
         <is>
-          <t>Unidentified Armed Group (Mali)</t>
+          <t>JNIM: Group for Support of Islam and Muslims ---- JNIM: Group for Support of Islam and Muslims</t>
         </is>
       </c>
       <c r="BG38" t="inlineStr"/>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>Civilians (Mali)</t>
+          <t>Civilians (Mali) ---- Civilians (Mali)</t>
         </is>
       </c>
       <c r="BI38" t="inlineStr">
         <is>
-          <t>Women (Mali)</t>
+          <t>Teachers (Mali) ---- Teachers (Mali)</t>
         </is>
       </c>
       <c r="BJ38" t="inlineStr">
         <is>
-          <t>On 27 June 2025, unidentified armed men went to the home of the principal of the local school in the village of Tabango (Ansongo, Gao). The principal was not at home and the gunmen beat his wife (no further details).</t>
+          <t>On 15 August 2024, JNIM abducted two school principals near the village of Arabebe (Niafunke, Tombouctou). ---- On 18 August 2024, JNIM militants killed two school principals in the village of Arabebe (Niafunke, Tombouctou). The lifeless bodies of the school principals were found near the village health center.</t>
         </is>
       </c>
       <c r="BK38" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2024-08-15 ---- 2024-08-18</t>
         </is>
       </c>
       <c r="BL38" t="inlineStr">
         <is>
-          <t>Ansongo</t>
+          <t>Niafunke</t>
         </is>
       </c>
       <c r="BM38" t="n">
-        <v>0.06684593430885725</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ML0702</t>
+          <t>ML0605</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -5956,7 +5928,7 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>ML0404</t>
+          <t>ML1001</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5965,37 +5937,37 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>50</v>
+        <v>36.8</v>
       </c>
       <c r="I39" t="n">
-        <v>35.6</v>
+        <v>61</v>
       </c>
       <c r="J39" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="K39" t="n">
-        <v>11.2</v>
+        <v>0.1</v>
       </c>
       <c r="L39" t="n">
-        <v>50</v>
+        <v>63.2</v>
       </c>
       <c r="M39" t="n">
-        <v>121.92</v>
+        <v>143.88</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>1.79</v>
+        <v>0.55</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.67</v>
+        <v>0.55</v>
       </c>
       <c r="R39" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -6004,13 +5976,13 @@
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>12.05</v>
+        <v>1.24</v>
       </c>
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="inlineStr"/>
@@ -6039,72 +6011,28 @@
       <c r="AV39" t="inlineStr"/>
       <c r="AW39" t="inlineStr"/>
       <c r="AX39" t="inlineStr"/>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t>Gao</t>
-        </is>
-      </c>
-      <c r="AZ39" t="n">
-        <v>3</v>
-      </c>
-      <c r="BA39" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB39" t="inlineStr">
-        <is>
-          <t>ML07</t>
-        </is>
-      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr"/>
+      <c r="BA39" t="inlineStr"/>
+      <c r="BB39" t="inlineStr"/>
       <c r="BC39" t="inlineStr"/>
-      <c r="BD39" t="inlineStr">
-        <is>
-          <t>Violence against civilians</t>
-        </is>
-      </c>
-      <c r="BE39" t="inlineStr">
-        <is>
-          <t>Attack</t>
-        </is>
-      </c>
-      <c r="BF39" t="inlineStr">
-        <is>
-          <t>Military Forces of Mali (2021-)</t>
-        </is>
-      </c>
-      <c r="BG39" t="inlineStr">
-        <is>
-          <t>Wagner Group</t>
-        </is>
-      </c>
-      <c r="BH39" t="inlineStr">
-        <is>
-          <t>Civilians (Mali)</t>
-        </is>
-      </c>
+      <c r="BD39" t="inlineStr"/>
+      <c r="BE39" t="inlineStr"/>
+      <c r="BF39" t="inlineStr"/>
+      <c r="BG39" t="inlineStr"/>
+      <c r="BH39" t="inlineStr"/>
       <c r="BI39" t="inlineStr"/>
-      <c r="BJ39" t="inlineStr">
-        <is>
-          <t>On 27 May 2024, FAMa and Wagner forces arrested 19 people identified by name including shepherds, village teachers, and traders in the village of Ersane, (Gao, Gao). The force also ransacked the village and arrested other shepherds who had come to water their animals. Three people died of asphyxiation, nine were released in Kidal, and 11 remain detained.</t>
-        </is>
-      </c>
-      <c r="BK39" t="inlineStr">
-        <is>
-          <t>2024-05-27</t>
-        </is>
-      </c>
-      <c r="BL39" t="inlineStr">
-        <is>
-          <t>Bourem</t>
-        </is>
-      </c>
+      <c r="BJ39" t="inlineStr"/>
+      <c r="BK39" t="inlineStr"/>
+      <c r="BL39" t="inlineStr"/>
       <c r="BM39" t="n">
-        <v>0.07333842627960276</v>
+        <v>0.09848373541770739</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ML0703</t>
+          <t>ML0701</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -6113,7 +6041,7 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>ML0701</t>
+          <t>ML0703</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -6122,22 +6050,22 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>58.2</v>
+        <v>58.8</v>
       </c>
       <c r="I40" t="n">
-        <v>41</v>
+        <v>39.9</v>
       </c>
       <c r="J40" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="K40" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="L40" t="n">
-        <v>41.8</v>
+        <v>41.2</v>
       </c>
       <c r="M40" t="n">
-        <v>194.11</v>
+        <v>142.17</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -6149,16 +6077,16 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>5.42</v>
       </c>
       <c r="R40" t="n">
-        <v>1.99</v>
+        <v>0.61</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
@@ -6167,7 +6095,7 @@
         <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>0.51</v>
+        <v>0.61</v>
       </c>
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr"/>
@@ -6202,10 +6130,10 @@
         </is>
       </c>
       <c r="AZ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA40" t="n">
         <v>1</v>
-      </c>
-      <c r="BA40" t="n">
-        <v>2</v>
       </c>
       <c r="BB40" t="inlineStr">
         <is>
@@ -6215,53 +6143,53 @@
       <c r="BC40" t="inlineStr"/>
       <c r="BD40" t="inlineStr">
         <is>
-          <t>Violence against civilians ---- Violence against civilians</t>
+          <t>Violence against civilians</t>
         </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
-          <t>Abduction/forced disappearance ---- Attack</t>
+          <t>Attack</t>
         </is>
       </c>
       <c r="BF40" t="inlineStr">
         <is>
-          <t>Unidentified Armed Group (Mali) ---- Unidentified Armed Group (Mali)</t>
+          <t>Unidentified Armed Group (Mali)</t>
         </is>
       </c>
       <c r="BG40" t="inlineStr"/>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>Civilians (Mali) ---- Civilians (Mali)</t>
+          <t>Civilians (Mali)</t>
         </is>
       </c>
       <c r="BI40" t="inlineStr">
         <is>
-          <t>Teachers (Mali) ---- Teachers (Mali)</t>
+          <t>Women (Mali)</t>
         </is>
       </c>
       <c r="BJ40" t="inlineStr">
         <is>
-          <t>On 26 April 2025, unidentified gunmen abducted a teacher and a resident in the village of Kobe (Gao, Gao). The gunmen claimed 3,000,000 CFA for their release. On 28 April 2025, they were released in exchange of payment (amount unknown). ---- On 5 June 2025, unidentified gunmen shot dead the principal of a secondary school in the village of Magnadoue (Gao, Gao). Seriously wounded in Magnadoue, he was taken to hospital in Gao, where he succumbed to his injuries.</t>
+          <t>On 27 June 2025, unidentified armed men went to the home of the principal of the local school in the village of Tabango (Ansongo, Gao). The principal was not at home and the gunmen beat his wife (no further details).</t>
         </is>
       </c>
       <c r="BK40" t="inlineStr">
         <is>
-          <t>2025-04-26 ---- 2025-06-05</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="BL40" t="inlineStr">
         <is>
-          <t>Gao</t>
+          <t>Ansongo</t>
         </is>
       </c>
       <c r="BM40" t="n">
-        <v>0.1273930826270106</v>
+        <v>0.06684593430885725</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ML0801</t>
+          <t>ML0702</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -6270,31 +6198,31 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>ML0303</t>
+          <t>ML0404</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>ML0104;ML0303;ML0801</t>
+          <t>ML0201;ML0204;ML0206;ML0305;ML0401;ML0403;ML0404;ML0406;ML0407;ML0505;ML0601;ML0605;ML0701;ML0702;ML0703;ML1001</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I41" t="n">
-        <v>100</v>
+        <v>35.6</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>11.2</v>
       </c>
       <c r="L41" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="M41" t="n">
-        <v>96.72</v>
+        <v>121.92</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -6303,13 +6231,13 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -6318,13 +6246,13 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>12.05</v>
       </c>
       <c r="X41" t="inlineStr"/>
       <c r="Y41" t="inlineStr"/>
@@ -6353,28 +6281,72 @@
       <c r="AV41" t="inlineStr"/>
       <c r="AW41" t="inlineStr"/>
       <c r="AX41" t="inlineStr"/>
-      <c r="AY41" t="inlineStr"/>
-      <c r="AZ41" t="inlineStr"/>
-      <c r="BA41" t="inlineStr"/>
-      <c r="BB41" t="inlineStr"/>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Gao</t>
+        </is>
+      </c>
+      <c r="AZ41" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB41" t="inlineStr">
+        <is>
+          <t>ML07</t>
+        </is>
+      </c>
       <c r="BC41" t="inlineStr"/>
-      <c r="BD41" t="inlineStr"/>
-      <c r="BE41" t="inlineStr"/>
-      <c r="BF41" t="inlineStr"/>
-      <c r="BG41" t="inlineStr"/>
-      <c r="BH41" t="inlineStr"/>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>Violence against civilians</t>
+        </is>
+      </c>
+      <c r="BE41" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="BF41" t="inlineStr">
+        <is>
+          <t>Military Forces of Mali (2021-)</t>
+        </is>
+      </c>
+      <c r="BG41" t="inlineStr">
+        <is>
+          <t>Wagner Group</t>
+        </is>
+      </c>
+      <c r="BH41" t="inlineStr">
+        <is>
+          <t>Civilians (Mali)</t>
+        </is>
+      </c>
       <c r="BI41" t="inlineStr"/>
-      <c r="BJ41" t="inlineStr"/>
-      <c r="BK41" t="inlineStr"/>
-      <c r="BL41" t="inlineStr"/>
+      <c r="BJ41" t="inlineStr">
+        <is>
+          <t>On 27 May 2024, FAMa and Wagner forces arrested 19 people identified by name including shepherds, village teachers, and traders in the village of Ersane, (Gao, Gao). The force also ransacked the village and arrested other shepherds who had come to water their animals. Three people died of asphyxiation, nine were released in Kidal, and 11 remain detained.</t>
+        </is>
+      </c>
+      <c r="BK41" t="inlineStr">
+        <is>
+          <t>2024-05-27</t>
+        </is>
+      </c>
+      <c r="BL41" t="inlineStr">
+        <is>
+          <t>Bourem</t>
+        </is>
+      </c>
       <c r="BM41" t="n">
-        <v>0</v>
+        <v>0.07333842627960276</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ML0802</t>
+          <t>ML0703</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -6383,61 +6355,61 @@
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>ML0102</t>
+          <t>ML0701</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>ML0102;ML0103;ML0106;ML0203;ML0304;ML0802</t>
+          <t>ML0201;ML0204;ML0206;ML0305;ML0401;ML0403;ML0404;ML0406;ML0407;ML0505;ML0601;ML0605;ML0701;ML0702;ML0703;ML1001</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>58.2</v>
       </c>
       <c r="I42" t="n">
-        <v>82.5</v>
+        <v>41</v>
       </c>
       <c r="J42" t="n">
-        <v>16.2</v>
+        <v>0.3</v>
       </c>
       <c r="K42" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="L42" t="n">
-        <v>100</v>
+        <v>41.8</v>
       </c>
       <c r="M42" t="n">
-        <v>81.25</v>
+        <v>194.11</v>
       </c>
       <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
         <v>1.25</v>
       </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" t="n">
-        <v>0</v>
-      </c>
       <c r="U42" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>13.75</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1.25</v>
+        <v>0.51</v>
       </c>
       <c r="X42" t="inlineStr"/>
       <c r="Y42" t="inlineStr"/>
@@ -6468,74 +6440,70 @@
       <c r="AX42" t="inlineStr"/>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>Kidal</t>
+          <t>Gao</t>
         </is>
       </c>
       <c r="AZ42" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA42" t="n">
         <v>2</v>
       </c>
-      <c r="BA42" t="n">
-        <v>1</v>
-      </c>
       <c r="BB42" t="inlineStr">
         <is>
-          <t>ML08</t>
+          <t>ML07</t>
         </is>
       </c>
       <c r="BC42" t="inlineStr"/>
       <c r="BD42" t="inlineStr">
         <is>
-          <t>Violence against civilians</t>
+          <t>Violence against civilians ---- Violence against civilians</t>
         </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>Abduction/forced disappearance ---- Attack</t>
         </is>
       </c>
       <c r="BF42" t="inlineStr">
         <is>
-          <t>Military Forces of Mali (2021-)</t>
-        </is>
-      </c>
-      <c r="BG42" t="inlineStr">
-        <is>
-          <t>Wagner Group</t>
-        </is>
-      </c>
+          <t>Unidentified Armed Group (Mali) ---- Unidentified Armed Group (Mali)</t>
+        </is>
+      </c>
+      <c r="BG42" t="inlineStr"/>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>Civilians (Mali)</t>
+          <t>Civilians (Mali) ---- Civilians (Mali)</t>
         </is>
       </c>
       <c r="BI42" t="inlineStr">
         <is>
-          <t>Teachers (Mali); Tuareg Ethnic Group (Mali)</t>
+          <t>Teachers (Mali) ---- Teachers (Mali)</t>
         </is>
       </c>
       <c r="BJ42" t="inlineStr">
         <is>
-          <t>On 22 April 2024, FAMa and Wagner forces killed two civilians from the Tuareg community including a teacher in the town of Kidal (Kidal, Kidal). They were arrested on November 2023 in Kidal town.</t>
+          <t>On 26 April 2025, unidentified gunmen abducted a teacher and a resident in the village of Kobe (Gao, Gao). The gunmen claimed 3,000,000 CFA for their release. On 28 April 2025, they were released in exchange of payment (amount unknown). ---- On 5 June 2025, unidentified gunmen shot dead the principal of a secondary school in the village of Magnadoue (Gao, Gao). Seriously wounded in Magnadoue, he was taken to hospital in Gao, where he succumbed to his injuries.</t>
         </is>
       </c>
       <c r="BK42" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2025-04-26 ---- 2025-06-05</t>
         </is>
       </c>
       <c r="BL42" t="inlineStr">
         <is>
-          <t>Kidal</t>
+          <t>Gao</t>
         </is>
       </c>
       <c r="BM42" t="n">
-        <v>0</v>
+        <v>0.1273930826270106</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ML0803</t>
+          <t>ML0801</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -6544,22 +6512,22 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>ML0107</t>
+          <t>ML0303</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>ML0107;ML0405;ML0501;ML0503;ML0508;ML0604;ML0803</t>
+          <t>ML0104;ML0303;ML0801</t>
         </is>
       </c>
       <c r="H43" t="n">
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>97.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="J43" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -6568,10 +6536,10 @@
         <v>100</v>
       </c>
       <c r="M43" t="n">
-        <v>95.70999999999999</v>
+        <v>96.72</v>
       </c>
       <c r="N43" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6595,7 +6563,7 @@
         <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
         <v>0</v>
@@ -6627,68 +6595,20 @@
       <c r="AV43" t="inlineStr"/>
       <c r="AW43" t="inlineStr"/>
       <c r="AX43" t="inlineStr"/>
-      <c r="AY43" t="inlineStr">
-        <is>
-          <t>Kidal</t>
-        </is>
-      </c>
-      <c r="AZ43" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA43" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB43" t="inlineStr">
-        <is>
-          <t>ML08</t>
-        </is>
-      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr"/>
+      <c r="BA43" t="inlineStr"/>
+      <c r="BB43" t="inlineStr"/>
       <c r="BC43" t="inlineStr"/>
-      <c r="BD43" t="inlineStr">
-        <is>
-          <t>Strategic developments ---- Violence against civilians ---- Strategic developments ---- Violence against civilians</t>
-        </is>
-      </c>
-      <c r="BE43" t="inlineStr">
-        <is>
-          <t>Arrests ---- Attack ---- Looting/property destruction ---- Attack</t>
-        </is>
-      </c>
-      <c r="BF43" t="inlineStr">
-        <is>
-          <t>Military Forces of Mali (2021-) ---- Military Forces of Mali (2021-) ---- Military Forces of Mali (2021-) ---- Military Forces of Mali (2021-)</t>
-        </is>
-      </c>
-      <c r="BG43" t="inlineStr">
-        <is>
-          <t>Wagner Group ---- Wagner Group ---- Wagner Group ---- Wagner Group</t>
-        </is>
-      </c>
-      <c r="BH43" t="inlineStr">
-        <is>
-          <t>Civilians (Mali) ---- Civilians (Mali) ---- Civilians (Mali) ---- Civilians (Mali)</t>
-        </is>
-      </c>
-      <c r="BI43" t="inlineStr">
-        <is>
-          <t>Teachers (Mali) ---- Teachers (Mali) ---- Labor Group (Mali) ---- Prisoners (Mali); Teachers (Mali)</t>
-        </is>
-      </c>
-      <c r="BJ43" t="inlineStr">
-        <is>
-          <t>On 24 April 2024, FAMa and Wagner arrested a teacher in the town of Tessalit (Tessalit, Kidal). ---- On 20 January 2025, FAMa and Wagner forces killed a teacher in the town of Aguelhok (Tessalit, Kidal). He was arrested on 18 January 2025 in the area of Gossi (Gourma-Rharous, Tombouctou). ---- Looting: On 25 January 2025, a FAMa and Wagner patrol looted shops, burned houses, arrested two civilians, including a teacher and a pharmacy manager, and damaged an Internet station in the village of Intechaq (Tessalit, Kidal). ---- Around 28 January 2025 (between 24 January - 1 February), FAMa and Wagner forces killed a teacher and her body was found near the village of Assamalmal (Tessalit, Kidal). He was arrested on 25 January 2025 in the village of Talabit.</t>
-        </is>
-      </c>
-      <c r="BK43" t="inlineStr">
-        <is>
-          <t>2024-04-24 ---- 2025-01-20 ---- 2025-01-25 ---- 2025-01-28</t>
-        </is>
-      </c>
-      <c r="BL43" t="inlineStr">
-        <is>
-          <t>Tessalit</t>
-        </is>
-      </c>
+      <c r="BD43" t="inlineStr"/>
+      <c r="BE43" t="inlineStr"/>
+      <c r="BF43" t="inlineStr"/>
+      <c r="BG43" t="inlineStr"/>
+      <c r="BH43" t="inlineStr"/>
+      <c r="BI43" t="inlineStr"/>
+      <c r="BJ43" t="inlineStr"/>
+      <c r="BK43" t="inlineStr"/>
+      <c r="BL43" t="inlineStr"/>
       <c r="BM43" t="n">
         <v>0</v>
       </c>
@@ -6696,7 +6616,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ML0804</t>
+          <t>ML0802</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -6705,34 +6625,34 @@
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>ML0307</t>
+          <t>ML0102</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>ML0307;ML0502;ML0804</t>
+          <t>ML0102;ML0103;ML0106;ML0203;ML0304;ML0802</t>
         </is>
       </c>
       <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="J44" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="K44" t="n">
         <v>1.2</v>
       </c>
-      <c r="I44" t="n">
-        <v>97</v>
-      </c>
-      <c r="J44" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
       <c r="L44" t="n">
-        <v>98.8</v>
+        <v>100</v>
       </c>
       <c r="M44" t="n">
-        <v>96.97</v>
+        <v>81.25</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6747,106 +6667,44 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>13.75</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
-      </c>
-      <c r="X44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="AP44" t="inlineStr">
-        <is>
-          <t>June 2024: A broken-down vehicle parked near a school was hit by a Malian airstrike, injuring a young boy.</t>
-        </is>
-      </c>
-      <c r="AQ44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Education Building </t>
-        </is>
-      </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="AS44" t="inlineStr">
-        <is>
-          <t>Mali Armed Forces</t>
-        </is>
-      </c>
-      <c r="AT44" t="inlineStr">
-        <is>
-          <t>Aerial Bomb: Plane</t>
-        </is>
-      </c>
-      <c r="AU44" t="inlineStr">
-        <is>
-          <t>School: No Further Details</t>
-        </is>
-      </c>
+        <v>1.25</v>
+      </c>
+      <c r="X44" t="inlineStr"/>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr"/>
+      <c r="AB44" t="inlineStr"/>
+      <c r="AC44" t="inlineStr"/>
+      <c r="AD44" t="inlineStr"/>
+      <c r="AE44" t="inlineStr"/>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="inlineStr"/>
+      <c r="AH44" t="inlineStr"/>
+      <c r="AI44" t="inlineStr"/>
+      <c r="AJ44" t="inlineStr"/>
+      <c r="AK44" t="inlineStr"/>
+      <c r="AL44" t="inlineStr"/>
+      <c r="AM44" t="inlineStr"/>
+      <c r="AN44" t="inlineStr"/>
+      <c r="AO44" t="inlineStr"/>
+      <c r="AP44" t="inlineStr"/>
+      <c r="AQ44" t="inlineStr"/>
+      <c r="AR44" t="inlineStr"/>
+      <c r="AS44" t="inlineStr"/>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AU44" t="inlineStr"/>
       <c r="AV44" t="inlineStr"/>
       <c r="AW44" t="inlineStr"/>
       <c r="AX44" t="inlineStr"/>
@@ -6856,10 +6714,10 @@
         </is>
       </c>
       <c r="AZ44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB44" t="inlineStr">
         <is>
@@ -6869,39 +6727,47 @@
       <c r="BC44" t="inlineStr"/>
       <c r="BD44" t="inlineStr">
         <is>
-          <t>Explosions/Remote violence ---- Explosions/Remote violence</t>
+          <t>Violence against civilians</t>
         </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
-          <t>Air/drone strike ---- Air/drone strike</t>
+          <t>Attack</t>
         </is>
       </c>
       <c r="BF44" t="inlineStr">
         <is>
-          <t>Military Forces of Mali (2021-) ---- Military Forces of Mali (2021-)</t>
-        </is>
-      </c>
-      <c r="BG44" t="inlineStr"/>
+          <t>Military Forces of Mali (2021-)</t>
+        </is>
+      </c>
+      <c r="BG44" t="inlineStr">
+        <is>
+          <t>Wagner Group</t>
+        </is>
+      </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>Civilians (Mali) ---- Civilians (Mali)</t>
-        </is>
-      </c>
-      <c r="BI44" t="inlineStr"/>
+          <t>Civilians (Mali)</t>
+        </is>
+      </c>
+      <c r="BI44" t="inlineStr">
+        <is>
+          <t>Teachers (Mali); Tuareg Ethnic Group (Mali)</t>
+        </is>
+      </c>
       <c r="BJ44" t="inlineStr">
         <is>
-          <t>On 19 June 2024, the Malian air force carried out an airstrike against a vehicle in the village of Tin Essako (Tin Essako, Kidal). The vehicle had broken down and was parked near a school. A young boy was injured. ---- On 1 October 2024, the Malian air force carried out a drone strike on a school in the village of Inakarot (Tin Essako, Kidal). Casualties unknown.</t>
+          <t>On 22 April 2024, FAMa and Wagner forces killed two civilians from the Tuareg community including a teacher in the town of Kidal (Kidal, Kidal). They were arrested on November 2023 in Kidal town.</t>
         </is>
       </c>
       <c r="BK44" t="inlineStr">
         <is>
-          <t>2024-06-19 ---- 2024-10-01</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="BL44" t="inlineStr">
         <is>
-          <t>Tin-Essako</t>
+          <t>Kidal</t>
         </is>
       </c>
       <c r="BM44" t="n">
@@ -6911,7 +6777,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ML0901</t>
+          <t>ML0803</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -6920,49 +6786,49 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>ML0504</t>
+          <t>ML0107</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>ML0504;ML0901</t>
+          <t>ML0107;ML0405;ML0501;ML0503;ML0508;ML0604;ML0803</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>23.9</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="J45" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>26</v>
+        <v>100</v>
       </c>
       <c r="M45" t="n">
-        <v>106.57</v>
+        <v>95.70999999999999</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>0.41</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
         <v>0</v>
@@ -6971,7 +6837,7 @@
         <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W45" t="n">
         <v>0</v>
@@ -7005,74 +6871,74 @@
       <c r="AX45" t="inlineStr"/>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>Bamako</t>
+          <t>Kidal</t>
         </is>
       </c>
       <c r="AZ45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA45" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BB45" t="inlineStr">
         <is>
-          <t>ML09</t>
+          <t>ML08</t>
         </is>
       </c>
       <c r="BC45" t="inlineStr"/>
       <c r="BD45" t="inlineStr">
         <is>
-          <t>Riots ---- Protests</t>
+          <t>Strategic developments ---- Violence against civilians ---- Strategic developments ---- Violence against civilians</t>
         </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
-          <t>Mob violence ---- Peaceful protest</t>
+          <t>Arrests ---- Attack ---- Looting/property destruction ---- Attack</t>
         </is>
       </c>
       <c r="BF45" t="inlineStr">
         <is>
-          <t>Rioters (Mali) ---- Protesters (Mali)</t>
+          <t>Military Forces of Mali (2021-) ---- Military Forces of Mali (2021-) ---- Military Forces of Mali (2021-) ---- Military Forces of Mali (2021-)</t>
         </is>
       </c>
       <c r="BG45" t="inlineStr">
         <is>
-          <t>AEEM: Association of Students and Pupils in Mali; Students (Mali) ---- Students (Mali)</t>
+          <t>Wagner Group ---- Wagner Group ---- Wagner Group ---- Wagner Group</t>
         </is>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>Rioters (Mali)</t>
+          <t>Civilians (Mali) ---- Civilians (Mali) ---- Civilians (Mali) ---- Civilians (Mali)</t>
         </is>
       </c>
       <c r="BI45" t="inlineStr">
         <is>
-          <t>AEEM: Association of Students and Pupils in Mali; Students (Mali)</t>
+          <t>Teachers (Mali) ---- Teachers (Mali) ---- Labor Group (Mali) ---- Prisoners (Mali); Teachers (Mali)</t>
         </is>
       </c>
       <c r="BJ45" t="inlineStr">
         <is>
-          <t>On 27 February 2024, two rival camps of the AEEM student organization clashed with stabbing weapons at the Badalabougou University in the city of Bamako (Bamako, Bamako). One student was killed. Following the incident, the Minister of Higher Education and Scientific Research suspended the activities of the coordinating office of the AEEM at the university until further notice. ---- On 28 May 2024, a number of students demonstrated peacefully in Kabala university campus in the city of Bamako (Bamako, Bamako) to denounce the water shortage in the campus.</t>
+          <t>On 24 April 2024, FAMa and Wagner arrested a teacher in the town of Tessalit (Tessalit, Kidal). ---- On 20 January 2025, FAMa and Wagner forces killed a teacher in the town of Aguelhok (Tessalit, Kidal). He was arrested on 18 January 2025 in the area of Gossi (Gourma-Rharous, Tombouctou). ---- Looting: On 25 January 2025, a FAMa and Wagner patrol looted shops, burned houses, arrested two civilians, including a teacher and a pharmacy manager, and damaged an Internet station in the village of Intechaq (Tessalit, Kidal). ---- Around 28 January 2025 (between 24 January - 1 February), FAMa and Wagner forces killed a teacher and her body was found near the village of Assamalmal (Tessalit, Kidal). He was arrested on 25 January 2025 in the village of Talabit.</t>
         </is>
       </c>
       <c r="BK45" t="inlineStr">
         <is>
-          <t>2024-02-27 ---- 2024-05-28</t>
+          <t>2024-04-24 ---- 2025-01-20 ---- 2025-01-25 ---- 2025-01-28</t>
         </is>
       </c>
       <c r="BL45" t="inlineStr">
         <is>
-          <t>Bamako</t>
+          <t>Tessalit</t>
         </is>
       </c>
       <c r="BM45" t="n">
-        <v>0.1605693852289919</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ML1001</t>
+          <t>ML0804</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -7081,49 +6947,49 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>ML0605</t>
+          <t>ML0307</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>ML0201;ML0204;ML0206;ML0305;ML0401;ML0403;ML0404;ML0406;ML0407;ML0505;ML0601;ML0605;ML0701;ML0702;ML0703;ML1001</t>
+          <t>ML0307;ML0502;ML0804</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>53.6</v>
+        <v>1.2</v>
       </c>
       <c r="I46" t="n">
-        <v>45.4</v>
+        <v>97</v>
       </c>
       <c r="J46" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="K46" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>46.4</v>
+        <v>98.8</v>
       </c>
       <c r="M46" t="n">
-        <v>111.01</v>
+        <v>96.97</v>
       </c>
       <c r="N46" t="n">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.39</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>0.5600000000000001</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>0.28</v>
+        <v>1.82</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -7132,97 +6998,473 @@
         <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>0.39</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="X46" t="inlineStr"/>
-      <c r="Y46" t="inlineStr"/>
-      <c r="Z46" t="inlineStr"/>
-      <c r="AA46" t="inlineStr"/>
-      <c r="AB46" t="inlineStr"/>
-      <c r="AC46" t="inlineStr"/>
-      <c r="AD46" t="inlineStr"/>
-      <c r="AE46" t="inlineStr"/>
-      <c r="AF46" t="inlineStr"/>
-      <c r="AG46" t="inlineStr"/>
-      <c r="AH46" t="inlineStr"/>
-      <c r="AI46" t="inlineStr"/>
-      <c r="AJ46" t="inlineStr"/>
-      <c r="AK46" t="inlineStr"/>
-      <c r="AL46" t="inlineStr"/>
-      <c r="AM46" t="inlineStr"/>
-      <c r="AN46" t="inlineStr"/>
-      <c r="AO46" t="inlineStr"/>
-      <c r="AP46" t="inlineStr"/>
-      <c r="AQ46" t="inlineStr"/>
-      <c r="AR46" t="inlineStr"/>
-      <c r="AS46" t="inlineStr"/>
-      <c r="AT46" t="inlineStr"/>
-      <c r="AU46" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AP46" t="inlineStr">
+        <is>
+          <t>June 2024: A broken-down vehicle parked near a school was hit by a Malian airstrike, injuring a young boy.</t>
+        </is>
+      </c>
+      <c r="AQ46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Education Building </t>
+        </is>
+      </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="AS46" t="inlineStr">
+        <is>
+          <t>Mali Armed Forces</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr">
+        <is>
+          <t>Aerial Bomb: Plane</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>School: No Further Details</t>
+        </is>
+      </c>
       <c r="AV46" t="inlineStr"/>
       <c r="AW46" t="inlineStr"/>
       <c r="AX46" t="inlineStr"/>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>Menaka</t>
+          <t>Kidal</t>
         </is>
       </c>
       <c r="AZ46" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BA46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB46" t="inlineStr">
         <is>
-          <t>ML10</t>
+          <t>ML08</t>
         </is>
       </c>
       <c r="BC46" t="inlineStr"/>
       <c r="BD46" t="inlineStr">
         <is>
-          <t>Battles</t>
+          <t>Explosions/Remote violence ---- Explosions/Remote violence</t>
         </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
-          <t>Armed clash</t>
+          <t>Air/drone strike ---- Air/drone strike</t>
         </is>
       </c>
       <c r="BF46" t="inlineStr">
         <is>
-          <t>Islamic State Sahel Province (ISSP)</t>
+          <t>Military Forces of Mali (2021-) ---- Military Forces of Mali (2021-)</t>
         </is>
       </c>
       <c r="BG46" t="inlineStr"/>
       <c r="BH46" t="inlineStr">
         <is>
+          <t>Civilians (Mali) ---- Civilians (Mali)</t>
+        </is>
+      </c>
+      <c r="BI46" t="inlineStr"/>
+      <c r="BJ46" t="inlineStr">
+        <is>
+          <t>On 19 June 2024, the Malian air force carried out an airstrike against a vehicle in the village of Tin Essako (Tin Essako, Kidal). The vehicle had broken down and was parked near a school. A young boy was injured. ---- On 1 October 2024, the Malian air force carried out a drone strike on a school in the village of Inakarot (Tin Essako, Kidal). Casualties unknown.</t>
+        </is>
+      </c>
+      <c r="BK46" t="inlineStr">
+        <is>
+          <t>2024-06-19 ---- 2024-10-01</t>
+        </is>
+      </c>
+      <c r="BL46" t="inlineStr">
+        <is>
+          <t>Tin-Essako</t>
+        </is>
+      </c>
+      <c r="BM46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ML0901</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>ML0504</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>ML0504;ML0901</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>74</v>
+      </c>
+      <c r="I47" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="J47" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>26</v>
+      </c>
+      <c r="M47" t="n">
+        <v>106.57</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" t="inlineStr"/>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr"/>
+      <c r="AB47" t="inlineStr"/>
+      <c r="AC47" t="inlineStr"/>
+      <c r="AD47" t="inlineStr"/>
+      <c r="AE47" t="inlineStr"/>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="inlineStr"/>
+      <c r="AH47" t="inlineStr"/>
+      <c r="AI47" t="inlineStr"/>
+      <c r="AJ47" t="inlineStr"/>
+      <c r="AK47" t="inlineStr"/>
+      <c r="AL47" t="inlineStr"/>
+      <c r="AM47" t="inlineStr"/>
+      <c r="AN47" t="inlineStr"/>
+      <c r="AO47" t="inlineStr"/>
+      <c r="AP47" t="inlineStr"/>
+      <c r="AQ47" t="inlineStr"/>
+      <c r="AR47" t="inlineStr"/>
+      <c r="AS47" t="inlineStr"/>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AU47" t="inlineStr"/>
+      <c r="AV47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr"/>
+      <c r="AX47" t="inlineStr"/>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Bamako</t>
+        </is>
+      </c>
+      <c r="AZ47" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA47" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB47" t="inlineStr">
+        <is>
+          <t>ML09</t>
+        </is>
+      </c>
+      <c r="BC47" t="inlineStr"/>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>Riots ---- Protests</t>
+        </is>
+      </c>
+      <c r="BE47" t="inlineStr">
+        <is>
+          <t>Mob violence ---- Peaceful protest</t>
+        </is>
+      </c>
+      <c r="BF47" t="inlineStr">
+        <is>
+          <t>Rioters (Mali) ---- Protesters (Mali)</t>
+        </is>
+      </c>
+      <c r="BG47" t="inlineStr">
+        <is>
+          <t>AEEM: Association of Students and Pupils in Mali; Students (Mali) ---- Students (Mali)</t>
+        </is>
+      </c>
+      <c r="BH47" t="inlineStr">
+        <is>
+          <t>Rioters (Mali)</t>
+        </is>
+      </c>
+      <c r="BI47" t="inlineStr">
+        <is>
+          <t>AEEM: Association of Students and Pupils in Mali; Students (Mali)</t>
+        </is>
+      </c>
+      <c r="BJ47" t="inlineStr">
+        <is>
+          <t>On 27 February 2024, two rival camps of the AEEM student organization clashed with stabbing weapons at the Badalabougou University in the city of Bamako (Bamako, Bamako). One student was killed. Following the incident, the Minister of Higher Education and Scientific Research suspended the activities of the coordinating office of the AEEM at the university until further notice. ---- On 28 May 2024, a number of students demonstrated peacefully in Kabala university campus in the city of Bamako (Bamako, Bamako) to denounce the water shortage in the campus.</t>
+        </is>
+      </c>
+      <c r="BK47" t="inlineStr">
+        <is>
+          <t>2024-02-27 ---- 2024-05-28</t>
+        </is>
+      </c>
+      <c r="BL47" t="inlineStr">
+        <is>
+          <t>Bamako</t>
+        </is>
+      </c>
+      <c r="BM47" t="n">
+        <v>0.1605693852289919</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ML1001</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>ML0605</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>ML0201;ML0204;ML0206;ML0305;ML0401;ML0403;ML0404;ML0406;ML0407;ML0505;ML0601;ML0605;ML0701;ML0702;ML0703;ML1001</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="I48" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L48" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="M48" t="n">
+        <v>111.01</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="X48" t="inlineStr"/>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr"/>
+      <c r="AB48" t="inlineStr"/>
+      <c r="AC48" t="inlineStr"/>
+      <c r="AD48" t="inlineStr"/>
+      <c r="AE48" t="inlineStr"/>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="inlineStr"/>
+      <c r="AH48" t="inlineStr"/>
+      <c r="AI48" t="inlineStr"/>
+      <c r="AJ48" t="inlineStr"/>
+      <c r="AK48" t="inlineStr"/>
+      <c r="AL48" t="inlineStr"/>
+      <c r="AM48" t="inlineStr"/>
+      <c r="AN48" t="inlineStr"/>
+      <c r="AO48" t="inlineStr"/>
+      <c r="AP48" t="inlineStr"/>
+      <c r="AQ48" t="inlineStr"/>
+      <c r="AR48" t="inlineStr"/>
+      <c r="AS48" t="inlineStr"/>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AU48" t="inlineStr"/>
+      <c r="AV48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr"/>
+      <c r="AX48" t="inlineStr"/>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Menaka</t>
+        </is>
+      </c>
+      <c r="AZ48" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA48" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB48" t="inlineStr">
+        <is>
+          <t>ML10</t>
+        </is>
+      </c>
+      <c r="BC48" t="inlineStr"/>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>Battles</t>
+        </is>
+      </c>
+      <c r="BE48" t="inlineStr">
+        <is>
+          <t>Armed clash</t>
+        </is>
+      </c>
+      <c r="BF48" t="inlineStr">
+        <is>
+          <t>Islamic State Sahel Province (ISSP)</t>
+        </is>
+      </c>
+      <c r="BG48" t="inlineStr"/>
+      <c r="BH48" t="inlineStr">
+        <is>
           <t>Military Forces of Mali (2021-)</t>
         </is>
       </c>
-      <c r="BI46" t="inlineStr">
+      <c r="BI48" t="inlineStr">
         <is>
           <t>GATIA: Imghad Tuareg and Allies Self-Defense Group; MSA: Movement for Azawad Salvation</t>
         </is>
       </c>
-      <c r="BJ46" t="inlineStr">
+      <c r="BJ48" t="inlineStr">
         <is>
           <t>On 2 January 2024, IS Sahel militants attacked a FAMa, GATIA and MSA checkpoint near the town of Menaka (Menaka, Menaka). The militants fired four shells at the town without causing any damage. FAMa stated the attack was repelled and three militants were killed, and airstrikes were conducted against the militants at the southwest area of Menaka. GATIA-MSA stated the attack was repelled and four militants were killed and several motorcycles destroyed, three GATIA-MSA militiamen were also killed the statement said. Trust sources said two schoolchildren were killed during the attack, GATIA-MSA one vehicle and two motorcycles were seized, and one FAMa vehicle was destroyed by the militants. 12 total fatalities coded. IS Sahel claimed responsibility, said it killed and wounded more than ten personnel, damaged a vehicle, and captured another vehicle, and various weapons and ammunition.</t>
         </is>
       </c>
-      <c r="BK46" t="inlineStr">
+      <c r="BK48" t="inlineStr">
         <is>
           <t>2024-01-02</t>
         </is>
       </c>
-      <c r="BL46" t="inlineStr">
+      <c r="BL48" t="inlineStr">
         <is>
           <t>Menaka</t>
         </is>
       </c>
-      <c r="BM46" t="n">
+      <c r="BM48" t="n">
         <v>0.5734549545929438</v>
       </c>
     </row>
@@ -7493,13 +7735,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15F59B28-F267-4FCE-AAE7-391593FB63B8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D423499B-A298-4D35-971F-4F117E6038FC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B859731-317D-483E-AECF-FA22B4D5CA40}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FDC7D9E1-2370-4BB1-BE9B-62F9E55AF6FF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F342E2B-043C-442B-90E3-145B24DB004E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48BA26CD-430E-4BCF-91CE-AFFEF01C06FC}"/>
 </file>